--- a/platform_PiN_output/Somalia___SOM/PiN_step2_Somalia___SOM_1022_04PM.xlsx
+++ b/platform_PiN_output/Somalia___SOM/PiN_step2_Somalia___SOM_1022_04PM.xlsx
@@ -153,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -239,7 +239,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -605,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="3" max="3"/>
@@ -624,11 +623,6 @@
     <col width="20" customWidth="1" min="18" max="18"/>
     <col width="33" customWidth="1" min="19" max="19"/>
     <col width="33" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="47" customWidth="1" min="22" max="22"/>
-    <col width="44" customWidth="1" min="23" max="23"/>
-    <col width="44" customWidth="1" min="24" max="24"/>
-    <col width="44" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -745,31 +739,6 @@
           <t># Tot PiN (severity levels 3-5)</t>
         </is>
       </c>
-      <c r="U5" s="6" t="inlineStr">
-        <is>
-          <t>Admin_Pcode_2024</t>
-        </is>
-      </c>
-      <c r="V5" s="6" t="inlineStr">
-        <is>
-          <t>%_severity_levels_1-2_2024_extrapolation_base</t>
-        </is>
-      </c>
-      <c r="W5" s="6" t="inlineStr">
-        <is>
-          <t>%_severity_level_3_2024_extrapolation_base</t>
-        </is>
-      </c>
-      <c r="X5" s="6" t="inlineStr">
-        <is>
-          <t>%_severity_level_4_2024_extrapolation_base</t>
-        </is>
-      </c>
-      <c r="Y5" s="6" t="inlineStr">
-        <is>
-          <t>%_severity_level_5_2024_extrapolation_base</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n"/>
@@ -785,7 +754,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>1144859</v>
+        <v>1742633</v>
       </c>
       <c r="F6" s="10" t="n"/>
       <c r="G6" s="10" t="n"/>
@@ -800,52 +769,37 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>1802376</v>
+        <v>2817988</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>36.5</v>
+        <v>38.2</v>
       </c>
       <c r="L6" s="9" t="n">
-        <v>657413</v>
+        <v>1075197</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>58.9</v>
+        <v>56.6</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>1061365</v>
+        <v>1594494</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>57811</v>
+        <v>109702</v>
       </c>
       <c r="Q6" s="9" t="n">
         <v>1.4</v>
       </c>
       <c r="R6" s="9" t="n">
-        <v>25683</v>
+        <v>38438</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>63.5</v>
+        <v>61.8</v>
       </c>
       <c r="T6" s="9" t="n">
-        <v>1144859</v>
-      </c>
-      <c r="U6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="9" t="n">
-        <v>0</v>
+        <v>1742633</v>
       </c>
     </row>
     <row r="7">
@@ -862,7 +816,7 @@
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>1000946</v>
+        <v>1571464</v>
       </c>
       <c r="F7" s="4" t="n"/>
       <c r="G7" s="4" t="n"/>
@@ -877,52 +831,37 @@
         </is>
       </c>
       <c r="J7" s="11" t="n">
-        <v>1628864</v>
+        <v>2609351</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>38.5</v>
+        <v>39.8</v>
       </c>
       <c r="L7" s="11" t="n">
-        <v>627819</v>
+        <v>1037720</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>57</v>
+        <v>55.1</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>928526</v>
+        <v>1438528</v>
       </c>
       <c r="O7" s="11" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="P7" s="11" t="n">
-        <v>49401</v>
+        <v>98009</v>
       </c>
       <c r="Q7" s="11" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="R7" s="11" t="n">
-        <v>23019</v>
+        <v>34927</v>
       </c>
       <c r="S7" s="11" t="n">
-        <v>61.5</v>
+        <v>60.2</v>
       </c>
       <c r="T7" s="11" t="n">
-        <v>1000946</v>
-      </c>
-      <c r="U7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="11" t="n">
-        <v>0</v>
+        <v>1571464</v>
       </c>
     </row>
     <row r="8">
@@ -939,7 +878,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>143913</v>
+        <v>171170</v>
       </c>
       <c r="F8" s="4" t="n"/>
       <c r="G8" s="4" t="n"/>
@@ -954,52 +893,37 @@
         </is>
       </c>
       <c r="J8" s="11" t="n">
-        <v>173512</v>
+        <v>208636</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>17.1</v>
+        <v>18</v>
       </c>
       <c r="L8" s="11" t="n">
-        <v>29595</v>
+        <v>37476</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>76.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="N8" s="11" t="n">
-        <v>132839</v>
+        <v>155966</v>
       </c>
       <c r="O8" s="11" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="P8" s="11" t="n">
-        <v>8410</v>
+        <v>11693</v>
       </c>
       <c r="Q8" s="11" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="R8" s="11" t="n">
-        <v>2664</v>
+        <v>3511</v>
       </c>
       <c r="S8" s="11" t="n">
-        <v>82.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="T8" s="11" t="n">
-        <v>143913</v>
-      </c>
-      <c r="U8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="11" t="n">
-        <v>0</v>
+        <v>171170</v>
       </c>
     </row>
     <row r="9">
@@ -1016,7 +940,7 @@
         </is>
       </c>
       <c r="E9" s="12" t="n">
-        <v>557341</v>
+        <v>848011</v>
       </c>
       <c r="F9" s="4" t="n"/>
       <c r="G9" s="4" t="n"/>
@@ -1033,11 +957,6 @@
       <c r="R9" s="2" t="n"/>
       <c r="S9" s="2" t="n"/>
       <c r="T9" s="2" t="n"/>
-      <c r="U9" s="2" t="n"/>
-      <c r="V9" s="2" t="n"/>
-      <c r="W9" s="2" t="n"/>
-      <c r="X9" s="2" t="n"/>
-      <c r="Y9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -1053,7 +972,7 @@
         </is>
       </c>
       <c r="E10" s="12" t="n">
-        <v>587517</v>
+        <v>894622</v>
       </c>
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n"/>
@@ -1070,11 +989,6 @@
       <c r="R10" s="2" t="n"/>
       <c r="S10" s="2" t="n"/>
       <c r="T10" s="2" t="n"/>
-      <c r="U10" s="2" t="n"/>
-      <c r="V10" s="2" t="n"/>
-      <c r="W10" s="2" t="n"/>
-      <c r="X10" s="2" t="n"/>
-      <c r="Y10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -1090,7 +1004,7 @@
         </is>
       </c>
       <c r="E11" s="13" t="n">
-        <v>88066</v>
+        <v>134049</v>
       </c>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
@@ -1107,11 +1021,6 @@
       <c r="R11" s="2" t="n"/>
       <c r="S11" s="2" t="n"/>
       <c r="T11" s="2" t="n"/>
-      <c r="U11" s="2" t="n"/>
-      <c r="V11" s="2" t="n"/>
-      <c r="W11" s="2" t="n"/>
-      <c r="X11" s="2" t="n"/>
-      <c r="Y11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -1127,7 +1036,7 @@
         </is>
       </c>
       <c r="E12" s="13" t="n">
-        <v>114486</v>
+        <v>174263</v>
       </c>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
@@ -1144,15 +1053,10 @@
       <c r="R12" s="2" t="n"/>
       <c r="S12" s="2" t="n"/>
       <c r="T12" s="2" t="n"/>
-      <c r="U12" s="2" t="n"/>
-      <c r="V12" s="2" t="n"/>
-      <c r="W12" s="2" t="n"/>
-      <c r="X12" s="2" t="n"/>
-      <c r="Y12" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C1:Y1"/>
+    <mergeCell ref="C1:T1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1164,7 +1068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Q60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -1270,41 +1174,41 @@
       <c r="D6" s="21" t="n"/>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>SO1103</t>
+          <t>SO1101</t>
         </is>
       </c>
       <c r="F6" s="22" t="n">
-        <v>17086</v>
+        <v>123388</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>40.8</v>
+        <v>60.1</v>
       </c>
       <c r="H6" s="23" t="n">
-        <v>6970</v>
+        <v>74156</v>
       </c>
       <c r="I6" s="24" t="n">
-        <v>53.5</v>
+        <v>35.5</v>
       </c>
       <c r="J6" s="24" t="n">
-        <v>9142</v>
+        <v>43803</v>
       </c>
       <c r="K6" s="25" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L6" s="25" t="n">
-        <v>718</v>
+        <v>5429</v>
       </c>
       <c r="M6" s="26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="N6" s="26" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="O6" s="27" t="n">
-        <v>59.1</v>
+        <v>39.9</v>
       </c>
       <c r="P6" s="27" t="n">
-        <v>10099</v>
+        <v>49232</v>
       </c>
       <c r="Q6" s="28" t="inlineStr">
         <is>
@@ -1319,29 +1223,29 @@
       <c r="D7" s="21" t="n"/>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>SO1104</t>
+          <t>SO1102</t>
         </is>
       </c>
       <c r="F7" s="22" t="n">
-        <v>15492</v>
+        <v>11059</v>
       </c>
       <c r="G7" s="23" t="n">
-        <v>37.8</v>
+        <v>64.5</v>
       </c>
       <c r="H7" s="23" t="n">
-        <v>5856</v>
+        <v>7133</v>
       </c>
       <c r="I7" s="24" t="n">
-        <v>55.2</v>
+        <v>33.2</v>
       </c>
       <c r="J7" s="24" t="n">
-        <v>8552</v>
+        <v>3672</v>
       </c>
       <c r="K7" s="25" t="n">
-        <v>7</v>
+        <v>2.4</v>
       </c>
       <c r="L7" s="25" t="n">
-        <v>1084</v>
+        <v>265</v>
       </c>
       <c r="M7" s="26" t="n">
         <v>0</v>
@@ -1350,10 +1254,10 @@
         <v>0</v>
       </c>
       <c r="O7" s="27" t="n">
-        <v>62.2</v>
+        <v>35.6</v>
       </c>
       <c r="P7" s="27" t="n">
-        <v>9636</v>
+        <v>3937</v>
       </c>
       <c r="Q7" s="28" t="inlineStr">
         <is>
@@ -1368,45 +1272,45 @@
       <c r="D8" s="21" t="n"/>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>SO1202</t>
+          <t>SO1103</t>
         </is>
       </c>
       <c r="F8" s="22" t="n">
-        <v>36044</v>
+        <v>17086</v>
       </c>
       <c r="G8" s="23" t="n">
-        <v>82.8</v>
+        <v>40.8</v>
       </c>
       <c r="H8" s="23" t="n">
-        <v>29845</v>
+        <v>6970</v>
       </c>
       <c r="I8" s="24" t="n">
-        <v>15.7</v>
+        <v>53.5</v>
       </c>
       <c r="J8" s="24" t="n">
-        <v>5659</v>
+        <v>9142</v>
       </c>
       <c r="K8" s="25" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="L8" s="25" t="n">
-        <v>433</v>
+        <v>718</v>
       </c>
       <c r="M8" s="26" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="N8" s="26" t="n">
-        <v>108</v>
+        <v>239</v>
       </c>
       <c r="O8" s="27" t="n">
-        <v>17.2</v>
+        <v>59.1</v>
       </c>
       <c r="P8" s="27" t="n">
-        <v>6200</v>
+        <v>10099</v>
       </c>
       <c r="Q8" s="28" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1417,29 +1321,29 @@
       <c r="D9" s="21" t="n"/>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>SO1304</t>
+          <t>SO1104</t>
         </is>
       </c>
       <c r="F9" s="22" t="n">
-        <v>23365</v>
+        <v>15492</v>
       </c>
       <c r="G9" s="23" t="n">
-        <v>42.9</v>
+        <v>37.8</v>
       </c>
       <c r="H9" s="23" t="n">
-        <v>10024</v>
+        <v>5856</v>
       </c>
       <c r="I9" s="24" t="n">
-        <v>47.2</v>
+        <v>55.2</v>
       </c>
       <c r="J9" s="24" t="n">
-        <v>11028</v>
+        <v>8552</v>
       </c>
       <c r="K9" s="25" t="n">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="L9" s="25" t="n">
-        <v>2290</v>
+        <v>1084</v>
       </c>
       <c r="M9" s="26" t="n">
         <v>0</v>
@@ -1448,10 +1352,10 @@
         <v>0</v>
       </c>
       <c r="O9" s="27" t="n">
-        <v>57</v>
+        <v>62.2</v>
       </c>
       <c r="P9" s="27" t="n">
-        <v>13318</v>
+        <v>9636</v>
       </c>
       <c r="Q9" s="28" t="inlineStr">
         <is>
@@ -1466,41 +1370,41 @@
       <c r="D10" s="21" t="n"/>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>SO1501</t>
+          <t>SO1201</t>
         </is>
       </c>
       <c r="F10" s="22" t="n">
-        <v>37338</v>
+        <v>187972</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>41.2</v>
+        <v>37.1</v>
       </c>
       <c r="H10" s="23" t="n">
-        <v>15375</v>
+        <v>69738</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>55.1</v>
+        <v>54.8</v>
       </c>
       <c r="J10" s="24" t="n">
-        <v>20588</v>
+        <v>103009</v>
       </c>
       <c r="K10" s="25" t="n">
-        <v>2</v>
+        <v>8.1</v>
       </c>
       <c r="L10" s="25" t="n">
-        <v>760</v>
+        <v>15226</v>
       </c>
       <c r="M10" s="26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="N10" s="26" t="n">
-        <v>608</v>
+        <v>0</v>
       </c>
       <c r="O10" s="27" t="n">
-        <v>58.8</v>
+        <v>62.9</v>
       </c>
       <c r="P10" s="27" t="n">
-        <v>21957</v>
+        <v>118234</v>
       </c>
       <c r="Q10" s="28" t="inlineStr">
         <is>
@@ -1515,45 +1419,45 @@
       <c r="D11" s="21" t="n"/>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>SO1503</t>
+          <t>SO1202</t>
         </is>
       </c>
       <c r="F11" s="22" t="n">
-        <v>32784</v>
+        <v>36044</v>
       </c>
       <c r="G11" s="23" t="n">
-        <v>25.4</v>
+        <v>82.8</v>
       </c>
       <c r="H11" s="23" t="n">
-        <v>8327</v>
+        <v>29845</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>73.09999999999999</v>
+        <v>15.7</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>23965</v>
+        <v>5659</v>
       </c>
       <c r="K11" s="25" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="L11" s="25" t="n">
-        <v>525</v>
+        <v>433</v>
       </c>
       <c r="M11" s="26" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="N11" s="26" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="O11" s="27" t="n">
-        <v>74.7</v>
+        <v>17.2</v>
       </c>
       <c r="P11" s="27" t="n">
-        <v>24490</v>
+        <v>6200</v>
       </c>
       <c r="Q11" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
@@ -1564,29 +1468,29 @@
       <c r="D12" s="21" t="n"/>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>SO1604</t>
+          <t>SO1304</t>
         </is>
       </c>
       <c r="F12" s="22" t="n">
-        <v>9184</v>
+        <v>23365</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>44</v>
+        <v>42.9</v>
       </c>
       <c r="H12" s="23" t="n">
-        <v>4041</v>
+        <v>10024</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>48.2</v>
+        <v>47.2</v>
       </c>
       <c r="J12" s="24" t="n">
-        <v>4427</v>
+        <v>11028</v>
       </c>
       <c r="K12" s="25" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L12" s="25" t="n">
-        <v>716</v>
+        <v>2290</v>
       </c>
       <c r="M12" s="26" t="n">
         <v>0</v>
@@ -1595,10 +1499,10 @@
         <v>0</v>
       </c>
       <c r="O12" s="27" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P12" s="27" t="n">
-        <v>5143</v>
+        <v>13318</v>
       </c>
       <c r="Q12" s="28" t="inlineStr">
         <is>
@@ -1613,41 +1517,41 @@
       <c r="D13" s="21" t="n"/>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t>SO1701</t>
+          <t>SO1401</t>
         </is>
       </c>
       <c r="F13" s="22" t="n">
-        <v>65054</v>
+        <v>52120</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>51.8</v>
+        <v>22.2</v>
       </c>
       <c r="H13" s="23" t="n">
-        <v>33707</v>
+        <v>11555</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>47.2</v>
+        <v>75.2</v>
       </c>
       <c r="J13" s="24" t="n">
-        <v>30681</v>
+        <v>39179</v>
       </c>
       <c r="K13" s="25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="L13" s="25" t="n">
-        <v>27</v>
+        <v>1379</v>
       </c>
       <c r="M13" s="26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" s="26" t="n">
-        <v>639</v>
+        <v>7</v>
       </c>
       <c r="O13" s="27" t="n">
-        <v>48.2</v>
+        <v>77.8</v>
       </c>
       <c r="P13" s="27" t="n">
-        <v>31347</v>
+        <v>40565</v>
       </c>
       <c r="Q13" s="28" t="inlineStr">
         <is>
@@ -1662,41 +1566,41 @@
       <c r="D14" s="21" t="n"/>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>SO1801</t>
+          <t>SO1501</t>
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>194353</v>
+        <v>37338</v>
       </c>
       <c r="G14" s="23" t="n">
-        <v>48.9</v>
+        <v>41.2</v>
       </c>
       <c r="H14" s="23" t="n">
-        <v>95038</v>
+        <v>15375</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>42.5</v>
+        <v>55.1</v>
       </c>
       <c r="J14" s="24" t="n">
-        <v>82507</v>
+        <v>20588</v>
       </c>
       <c r="K14" s="25" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="L14" s="25" t="n">
-        <v>7068</v>
+        <v>760</v>
       </c>
       <c r="M14" s="26" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="N14" s="26" t="n">
-        <v>9741</v>
+        <v>608</v>
       </c>
       <c r="O14" s="27" t="n">
-        <v>51.1</v>
+        <v>58.8</v>
       </c>
       <c r="P14" s="27" t="n">
-        <v>99315</v>
+        <v>21957</v>
       </c>
       <c r="Q14" s="28" t="inlineStr">
         <is>
@@ -1711,41 +1615,41 @@
       <c r="D15" s="21" t="n"/>
       <c r="E15" s="22" t="inlineStr">
         <is>
-          <t>SO1802</t>
+          <t>SO1502</t>
         </is>
       </c>
       <c r="F15" s="22" t="n">
-        <v>37221</v>
+        <v>19315</v>
       </c>
       <c r="G15" s="23" t="n">
-        <v>69.7</v>
+        <v>62.2</v>
       </c>
       <c r="H15" s="23" t="n">
-        <v>25953</v>
+        <v>12014</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>29</v>
+        <v>37.1</v>
       </c>
       <c r="J15" s="24" t="n">
-        <v>10811</v>
+        <v>7166</v>
       </c>
       <c r="K15" s="25" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="L15" s="25" t="n">
-        <v>439</v>
+        <v>58</v>
       </c>
       <c r="M15" s="26" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="N15" s="26" t="n">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="O15" s="27" t="n">
-        <v>30.3</v>
+        <v>37.7</v>
       </c>
       <c r="P15" s="27" t="n">
-        <v>11269</v>
+        <v>7282</v>
       </c>
       <c r="Q15" s="28" t="inlineStr">
         <is>
@@ -1760,29 +1664,29 @@
       <c r="D16" s="21" t="n"/>
       <c r="E16" s="22" t="inlineStr">
         <is>
-          <t>SO1803</t>
+          <t>SO1503</t>
         </is>
       </c>
       <c r="F16" s="22" t="n">
-        <v>46927</v>
+        <v>32784</v>
       </c>
       <c r="G16" s="23" t="n">
-        <v>35.3</v>
+        <v>25.4</v>
       </c>
       <c r="H16" s="23" t="n">
-        <v>16571</v>
+        <v>8327</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>62.9</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="J16" s="24" t="n">
-        <v>29512</v>
+        <v>23965</v>
       </c>
       <c r="K16" s="25" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="L16" s="25" t="n">
-        <v>844</v>
+        <v>525</v>
       </c>
       <c r="M16" s="26" t="n">
         <v>0</v>
@@ -1791,10 +1695,10 @@
         <v>0</v>
       </c>
       <c r="O16" s="27" t="n">
-        <v>64.7</v>
+        <v>74.7</v>
       </c>
       <c r="P16" s="27" t="n">
-        <v>30356</v>
+        <v>24490</v>
       </c>
       <c r="Q16" s="28" t="inlineStr">
         <is>
@@ -1809,41 +1713,41 @@
       <c r="D17" s="21" t="n"/>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>SO1901</t>
+          <t>SO1601</t>
         </is>
       </c>
       <c r="F17" s="22" t="n">
-        <v>64552</v>
+        <v>149286</v>
       </c>
       <c r="G17" s="23" t="n">
-        <v>25.3</v>
+        <v>34.1</v>
       </c>
       <c r="H17" s="23" t="n">
-        <v>16359</v>
+        <v>50947</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>60</v>
+        <v>65.2</v>
       </c>
       <c r="J17" s="24" t="n">
-        <v>38749</v>
+        <v>97380</v>
       </c>
       <c r="K17" s="25" t="n">
-        <v>14.6</v>
+        <v>0.1</v>
       </c>
       <c r="L17" s="25" t="n">
-        <v>9445</v>
+        <v>91</v>
       </c>
       <c r="M17" s="26" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="N17" s="26" t="n">
-        <v>0</v>
+        <v>875</v>
       </c>
       <c r="O17" s="27" t="n">
-        <v>74.7</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="P17" s="27" t="n">
-        <v>48193</v>
+        <v>98346</v>
       </c>
       <c r="Q17" s="28" t="inlineStr">
         <is>
@@ -1858,41 +1762,41 @@
       <c r="D18" s="21" t="n"/>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>SO1902</t>
+          <t>SO1602</t>
         </is>
       </c>
       <c r="F18" s="22" t="n">
-        <v>51869</v>
+        <v>9550</v>
       </c>
       <c r="G18" s="23" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
       <c r="H18" s="23" t="n">
-        <v>23675</v>
+        <v>4345</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>51.9</v>
+        <v>54</v>
       </c>
       <c r="J18" s="24" t="n">
-        <v>26942</v>
+        <v>5157</v>
       </c>
       <c r="K18" s="25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="L18" s="25" t="n">
-        <v>1095</v>
+        <v>0</v>
       </c>
       <c r="M18" s="26" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="N18" s="26" t="n">
-        <v>207</v>
+        <v>48</v>
       </c>
       <c r="O18" s="27" t="n">
         <v>54.5</v>
       </c>
       <c r="P18" s="27" t="n">
-        <v>28244</v>
+        <v>5205</v>
       </c>
       <c r="Q18" s="28" t="inlineStr">
         <is>
@@ -1907,41 +1811,41 @@
       <c r="D19" s="21" t="n"/>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>SO1903</t>
+          <t>SO1603</t>
         </is>
       </c>
       <c r="F19" s="22" t="n">
-        <v>34292</v>
+        <v>17619</v>
       </c>
       <c r="G19" s="23" t="n">
-        <v>36</v>
+        <v>42.4</v>
       </c>
       <c r="H19" s="23" t="n">
-        <v>12334</v>
+        <v>7471</v>
       </c>
       <c r="I19" s="24" t="n">
-        <v>62.2</v>
+        <v>55.3</v>
       </c>
       <c r="J19" s="24" t="n">
-        <v>21340</v>
+        <v>9743</v>
       </c>
       <c r="K19" s="25" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="L19" s="25" t="n">
-        <v>171</v>
+        <v>405</v>
       </c>
       <c r="M19" s="26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="N19" s="26" t="n">
-        <v>481</v>
+        <v>0</v>
       </c>
       <c r="O19" s="27" t="n">
-        <v>64.09999999999999</v>
+        <v>57.6</v>
       </c>
       <c r="P19" s="27" t="n">
-        <v>21992</v>
+        <v>10149</v>
       </c>
       <c r="Q19" s="28" t="inlineStr">
         <is>
@@ -1956,41 +1860,41 @@
       <c r="D20" s="21" t="n"/>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>SO2001</t>
+          <t>SO1604</t>
         </is>
       </c>
       <c r="F20" s="22" t="n">
-        <v>67859</v>
+        <v>9184</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>30.4</v>
+        <v>44</v>
       </c>
       <c r="H20" s="23" t="n">
-        <v>20623</v>
+        <v>4041</v>
       </c>
       <c r="I20" s="24" t="n">
-        <v>67.3</v>
+        <v>48.2</v>
       </c>
       <c r="J20" s="24" t="n">
-        <v>45697</v>
+        <v>4427</v>
       </c>
       <c r="K20" s="25" t="n">
-        <v>2.1</v>
+        <v>7.8</v>
       </c>
       <c r="L20" s="25" t="n">
-        <v>1394</v>
+        <v>716</v>
       </c>
       <c r="M20" s="26" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N20" s="26" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="O20" s="27" t="n">
-        <v>69.59999999999999</v>
+        <v>56</v>
       </c>
       <c r="P20" s="27" t="n">
-        <v>47237</v>
+        <v>5143</v>
       </c>
       <c r="Q20" s="28" t="inlineStr">
         <is>
@@ -2005,41 +1909,41 @@
       <c r="D21" s="21" t="n"/>
       <c r="E21" s="22" t="inlineStr">
         <is>
-          <t>SO2002</t>
+          <t>SO1606</t>
         </is>
       </c>
       <c r="F21" s="22" t="n">
-        <v>16974</v>
+        <v>31417</v>
       </c>
       <c r="G21" s="23" t="n">
-        <v>10.3</v>
+        <v>33.6</v>
       </c>
       <c r="H21" s="23" t="n">
-        <v>1746</v>
+        <v>10546</v>
       </c>
       <c r="I21" s="24" t="n">
-        <v>80.40000000000001</v>
+        <v>62.7</v>
       </c>
       <c r="J21" s="24" t="n">
-        <v>13653</v>
+        <v>19707</v>
       </c>
       <c r="K21" s="25" t="n">
-        <v>7.6</v>
+        <v>2.5</v>
       </c>
       <c r="L21" s="25" t="n">
-        <v>1291</v>
+        <v>791</v>
       </c>
       <c r="M21" s="26" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="N21" s="26" t="n">
-        <v>290</v>
+        <v>401</v>
       </c>
       <c r="O21" s="27" t="n">
-        <v>89.7</v>
+        <v>66.5</v>
       </c>
       <c r="P21" s="27" t="n">
-        <v>15233</v>
+        <v>20900</v>
       </c>
       <c r="Q21" s="28" t="inlineStr">
         <is>
@@ -2054,41 +1958,41 @@
       <c r="D22" s="21" t="n"/>
       <c r="E22" s="22" t="inlineStr">
         <is>
-          <t>SO2003</t>
+          <t>SO1701</t>
         </is>
       </c>
       <c r="F22" s="22" t="n">
-        <v>10921</v>
+        <v>65054</v>
       </c>
       <c r="G22" s="23" t="n">
-        <v>44.8</v>
+        <v>51.8</v>
       </c>
       <c r="H22" s="23" t="n">
-        <v>4893</v>
+        <v>33707</v>
       </c>
       <c r="I22" s="24" t="n">
-        <v>53.2</v>
+        <v>47.2</v>
       </c>
       <c r="J22" s="24" t="n">
-        <v>5807</v>
+        <v>30681</v>
       </c>
       <c r="K22" s="25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="L22" s="25" t="n">
-        <v>224</v>
+        <v>27</v>
       </c>
       <c r="M22" s="26" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="N22" s="26" t="n">
-        <v>7</v>
+        <v>639</v>
       </c>
       <c r="O22" s="27" t="n">
-        <v>55.3</v>
+        <v>48.2</v>
       </c>
       <c r="P22" s="27" t="n">
-        <v>6038</v>
+        <v>31347</v>
       </c>
       <c r="Q22" s="28" t="inlineStr">
         <is>
@@ -2103,41 +2007,41 @@
       <c r="D23" s="21" t="n"/>
       <c r="E23" s="22" t="inlineStr">
         <is>
-          <t>SO2101</t>
+          <t>SO1702</t>
         </is>
       </c>
       <c r="F23" s="22" t="n">
-        <v>57048</v>
+        <v>24113</v>
       </c>
       <c r="G23" s="23" t="n">
-        <v>3.6</v>
+        <v>29.5</v>
       </c>
       <c r="H23" s="23" t="n">
-        <v>2073</v>
+        <v>7113</v>
       </c>
       <c r="I23" s="24" t="n">
-        <v>90.5</v>
+        <v>70.2</v>
       </c>
       <c r="J23" s="24" t="n">
-        <v>51603</v>
+        <v>16927</v>
       </c>
       <c r="K23" s="25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L23" s="25" t="n">
-        <v>2832</v>
+        <v>0</v>
       </c>
       <c r="M23" s="26" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="N23" s="26" t="n">
-        <v>573</v>
+        <v>72</v>
       </c>
       <c r="O23" s="27" t="n">
-        <v>96.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="P23" s="27" t="n">
-        <v>55009</v>
+        <v>17000</v>
       </c>
       <c r="Q23" s="28" t="inlineStr">
         <is>
@@ -2152,41 +2056,41 @@
       <c r="D24" s="21" t="n"/>
       <c r="E24" s="22" t="inlineStr">
         <is>
-          <t>SO2203</t>
+          <t>SO1801</t>
         </is>
       </c>
       <c r="F24" s="22" t="n">
-        <v>247922</v>
+        <v>194353</v>
       </c>
       <c r="G24" s="23" t="n">
-        <v>31.4</v>
+        <v>48.9</v>
       </c>
       <c r="H24" s="23" t="n">
-        <v>77848</v>
+        <v>95038</v>
       </c>
       <c r="I24" s="24" t="n">
-        <v>68.2</v>
+        <v>42.5</v>
       </c>
       <c r="J24" s="24" t="n">
-        <v>169083</v>
+        <v>82507</v>
       </c>
       <c r="K24" s="25" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="L24" s="25" t="n">
-        <v>744</v>
+        <v>7068</v>
       </c>
       <c r="M24" s="26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N24" s="26" t="n">
-        <v>0</v>
+        <v>9741</v>
       </c>
       <c r="O24" s="27" t="n">
-        <v>68.5</v>
+        <v>51.1</v>
       </c>
       <c r="P24" s="27" t="n">
-        <v>169827</v>
+        <v>99315</v>
       </c>
       <c r="Q24" s="28" t="inlineStr">
         <is>
@@ -2201,41 +2105,41 @@
       <c r="D25" s="21" t="n"/>
       <c r="E25" s="22" t="inlineStr">
         <is>
-          <t>SO2210</t>
+          <t>SO1802</t>
         </is>
       </c>
       <c r="F25" s="22" t="n">
-        <v>171981</v>
+        <v>37221</v>
       </c>
       <c r="G25" s="23" t="n">
-        <v>35.8</v>
+        <v>69.7</v>
       </c>
       <c r="H25" s="23" t="n">
-        <v>61569</v>
+        <v>25953</v>
       </c>
       <c r="I25" s="24" t="n">
-        <v>59.8</v>
+        <v>29</v>
       </c>
       <c r="J25" s="24" t="n">
-        <v>102845</v>
+        <v>10811</v>
       </c>
       <c r="K25" s="25" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="L25" s="25" t="n">
-        <v>6363</v>
+        <v>439</v>
       </c>
       <c r="M25" s="26" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="N25" s="26" t="n">
-        <v>1204</v>
+        <v>20</v>
       </c>
       <c r="O25" s="27" t="n">
-        <v>64.2</v>
+        <v>30.3</v>
       </c>
       <c r="P25" s="27" t="n">
-        <v>110412</v>
+        <v>11269</v>
       </c>
       <c r="Q25" s="28" t="inlineStr">
         <is>
@@ -2250,41 +2154,41 @@
       <c r="D26" s="21" t="n"/>
       <c r="E26" s="22" t="inlineStr">
         <is>
-          <t>SO2301</t>
+          <t>SO1803</t>
         </is>
       </c>
       <c r="F26" s="22" t="n">
-        <v>60255</v>
+        <v>46927</v>
       </c>
       <c r="G26" s="23" t="n">
-        <v>61.1</v>
+        <v>35.3</v>
       </c>
       <c r="H26" s="23" t="n">
-        <v>36790</v>
+        <v>16571</v>
       </c>
       <c r="I26" s="24" t="n">
-        <v>38.3</v>
+        <v>62.9</v>
       </c>
       <c r="J26" s="24" t="n">
-        <v>23104</v>
+        <v>29512</v>
       </c>
       <c r="K26" s="25" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="L26" s="25" t="n">
-        <v>181</v>
+        <v>844</v>
       </c>
       <c r="M26" s="26" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="N26" s="26" t="n">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="O26" s="27" t="n">
-        <v>38.9</v>
+        <v>64.7</v>
       </c>
       <c r="P26" s="27" t="n">
-        <v>23465</v>
+        <v>30356</v>
       </c>
       <c r="Q26" s="28" t="inlineStr">
         <is>
@@ -2299,41 +2203,41 @@
       <c r="D27" s="21" t="n"/>
       <c r="E27" s="22" t="inlineStr">
         <is>
-          <t>SO2302</t>
+          <t>SO1804</t>
         </is>
       </c>
       <c r="F27" s="22" t="n">
-        <v>74165</v>
+        <v>44874</v>
       </c>
       <c r="G27" s="23" t="n">
-        <v>13.9</v>
+        <v>38.3</v>
       </c>
       <c r="H27" s="23" t="n">
-        <v>10343</v>
+        <v>17187</v>
       </c>
       <c r="I27" s="24" t="n">
-        <v>83.7</v>
+        <v>54.7</v>
       </c>
       <c r="J27" s="24" t="n">
-        <v>62098</v>
+        <v>24546</v>
       </c>
       <c r="K27" s="25" t="n">
-        <v>0.6</v>
+        <v>7</v>
       </c>
       <c r="L27" s="25" t="n">
-        <v>427</v>
+        <v>3141</v>
       </c>
       <c r="M27" s="26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="N27" s="26" t="n">
-        <v>1290</v>
+        <v>0</v>
       </c>
       <c r="O27" s="27" t="n">
-        <v>86</v>
+        <v>61.7</v>
       </c>
       <c r="P27" s="27" t="n">
-        <v>63816</v>
+        <v>27687</v>
       </c>
       <c r="Q27" s="28" t="inlineStr">
         <is>
@@ -2348,41 +2252,41 @@
       <c r="D28" s="21" t="n"/>
       <c r="E28" s="22" t="inlineStr">
         <is>
-          <t>SO2401</t>
+          <t>SO1901</t>
         </is>
       </c>
       <c r="F28" s="22" t="n">
-        <v>176201</v>
+        <v>64552</v>
       </c>
       <c r="G28" s="23" t="n">
-        <v>35.7</v>
+        <v>25.3</v>
       </c>
       <c r="H28" s="23" t="n">
-        <v>62903</v>
+        <v>16359</v>
       </c>
       <c r="I28" s="24" t="n">
-        <v>59.6</v>
+        <v>60</v>
       </c>
       <c r="J28" s="24" t="n">
-        <v>104965</v>
+        <v>38749</v>
       </c>
       <c r="K28" s="25" t="n">
-        <v>3.5</v>
+        <v>14.6</v>
       </c>
       <c r="L28" s="25" t="n">
-        <v>6144</v>
+        <v>9445</v>
       </c>
       <c r="M28" s="26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="N28" s="26" t="n">
-        <v>2188</v>
+        <v>0</v>
       </c>
       <c r="O28" s="27" t="n">
-        <v>64.3</v>
+        <v>74.7</v>
       </c>
       <c r="P28" s="27" t="n">
-        <v>113298</v>
+        <v>48193</v>
       </c>
       <c r="Q28" s="28" t="inlineStr">
         <is>
@@ -2397,41 +2301,41 @@
       <c r="D29" s="21" t="n"/>
       <c r="E29" s="22" t="inlineStr">
         <is>
-          <t>SO2402</t>
+          <t>SO1902</t>
         </is>
       </c>
       <c r="F29" s="22" t="n">
-        <v>39025</v>
+        <v>51869</v>
       </c>
       <c r="G29" s="23" t="n">
-        <v>27.2</v>
+        <v>45.6</v>
       </c>
       <c r="H29" s="23" t="n">
-        <v>10599</v>
+        <v>23675</v>
       </c>
       <c r="I29" s="24" t="n">
-        <v>65</v>
+        <v>51.9</v>
       </c>
       <c r="J29" s="24" t="n">
-        <v>25380</v>
+        <v>26942</v>
       </c>
       <c r="K29" s="25" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="L29" s="25" t="n">
-        <v>655</v>
+        <v>1095</v>
       </c>
       <c r="M29" s="26" t="n">
-        <v>6.1</v>
+        <v>0.4</v>
       </c>
       <c r="N29" s="26" t="n">
-        <v>2392</v>
+        <v>207</v>
       </c>
       <c r="O29" s="27" t="n">
-        <v>72.8</v>
+        <v>54.5</v>
       </c>
       <c r="P29" s="27" t="n">
-        <v>28427</v>
+        <v>28244</v>
       </c>
       <c r="Q29" s="28" t="inlineStr">
         <is>
@@ -2446,41 +2350,41 @@
       <c r="D30" s="21" t="n"/>
       <c r="E30" s="22" t="inlineStr">
         <is>
-          <t>SO2403</t>
+          <t>SO1903</t>
         </is>
       </c>
       <c r="F30" s="22" t="n">
-        <v>36097</v>
+        <v>34292</v>
       </c>
       <c r="G30" s="23" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="H30" s="23" t="n">
-        <v>1811</v>
+        <v>12334</v>
       </c>
       <c r="I30" s="24" t="n">
-        <v>89.90000000000001</v>
+        <v>62.2</v>
       </c>
       <c r="J30" s="24" t="n">
-        <v>32462</v>
+        <v>21340</v>
       </c>
       <c r="K30" s="25" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="L30" s="25" t="n">
-        <v>485</v>
+        <v>171</v>
       </c>
       <c r="M30" s="26" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="N30" s="26" t="n">
-        <v>1365</v>
+        <v>481</v>
       </c>
       <c r="O30" s="27" t="n">
-        <v>95.09999999999999</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="P30" s="27" t="n">
-        <v>34313</v>
+        <v>21992</v>
       </c>
       <c r="Q30" s="28" t="inlineStr">
         <is>
@@ -2495,41 +2399,41 @@
       <c r="D31" s="21" t="n"/>
       <c r="E31" s="22" t="inlineStr">
         <is>
-          <t>SO2404</t>
+          <t>SO2001</t>
         </is>
       </c>
       <c r="F31" s="22" t="n">
-        <v>30823</v>
+        <v>67859</v>
       </c>
       <c r="G31" s="23" t="n">
-        <v>47.6</v>
+        <v>30.4</v>
       </c>
       <c r="H31" s="23" t="n">
-        <v>14683</v>
+        <v>20623</v>
       </c>
       <c r="I31" s="24" t="n">
-        <v>47.2</v>
+        <v>67.3</v>
       </c>
       <c r="J31" s="24" t="n">
-        <v>14548</v>
+        <v>45697</v>
       </c>
       <c r="K31" s="25" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="L31" s="25" t="n">
-        <v>382</v>
+        <v>1394</v>
       </c>
       <c r="M31" s="26" t="n">
-        <v>3.9</v>
+        <v>0.2</v>
       </c>
       <c r="N31" s="26" t="n">
-        <v>1205</v>
+        <v>146</v>
       </c>
       <c r="O31" s="27" t="n">
-        <v>52.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="P31" s="27" t="n">
-        <v>16134</v>
+        <v>47237</v>
       </c>
       <c r="Q31" s="28" t="inlineStr">
         <is>
@@ -2544,41 +2448,41 @@
       <c r="D32" s="21" t="n"/>
       <c r="E32" s="22" t="inlineStr">
         <is>
-          <t>SO2504</t>
+          <t>SO2002</t>
         </is>
       </c>
       <c r="F32" s="22" t="n">
-        <v>17438</v>
+        <v>16974</v>
       </c>
       <c r="G32" s="23" t="n">
-        <v>54.5</v>
+        <v>10.3</v>
       </c>
       <c r="H32" s="23" t="n">
-        <v>9498</v>
+        <v>1746</v>
       </c>
       <c r="I32" s="24" t="n">
-        <v>45.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="J32" s="24" t="n">
-        <v>7940</v>
+        <v>13653</v>
       </c>
       <c r="K32" s="25" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="L32" s="25" t="n">
-        <v>0</v>
+        <v>1291</v>
       </c>
       <c r="M32" s="26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="N32" s="26" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="O32" s="27" t="n">
-        <v>45.5</v>
+        <v>89.7</v>
       </c>
       <c r="P32" s="27" t="n">
-        <v>7940</v>
+        <v>15233</v>
       </c>
       <c r="Q32" s="28" t="inlineStr">
         <is>
@@ -2593,41 +2497,41 @@
       <c r="D33" s="21" t="n"/>
       <c r="E33" s="22" t="inlineStr">
         <is>
-          <t>SO2602</t>
+          <t>SO2003</t>
         </is>
       </c>
       <c r="F33" s="22" t="n">
-        <v>37431</v>
+        <v>10921</v>
       </c>
       <c r="G33" s="23" t="n">
-        <v>37.3</v>
+        <v>44.8</v>
       </c>
       <c r="H33" s="23" t="n">
-        <v>13968</v>
+        <v>4893</v>
       </c>
       <c r="I33" s="24" t="n">
-        <v>56.7</v>
+        <v>53.2</v>
       </c>
       <c r="J33" s="24" t="n">
-        <v>21205</v>
+        <v>5807</v>
       </c>
       <c r="K33" s="25" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="L33" s="25" t="n">
-        <v>1589</v>
+        <v>224</v>
       </c>
       <c r="M33" s="26" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="N33" s="26" t="n">
-        <v>658</v>
+        <v>7</v>
       </c>
       <c r="O33" s="27" t="n">
-        <v>62.7</v>
+        <v>55.3</v>
       </c>
       <c r="P33" s="27" t="n">
-        <v>23452</v>
+        <v>6038</v>
       </c>
       <c r="Q33" s="28" t="inlineStr">
         <is>
@@ -2642,41 +2546,41 @@
       <c r="D34" s="21" t="n"/>
       <c r="E34" s="22" t="inlineStr">
         <is>
-          <t>SO2603</t>
+          <t>SO2101</t>
         </is>
       </c>
       <c r="F34" s="22" t="n">
-        <v>18703</v>
+        <v>57048</v>
       </c>
       <c r="G34" s="23" t="n">
-        <v>6.9</v>
+        <v>3.6</v>
       </c>
       <c r="H34" s="23" t="n">
-        <v>1297</v>
+        <v>2073</v>
       </c>
       <c r="I34" s="24" t="n">
-        <v>81.5</v>
+        <v>90.5</v>
       </c>
       <c r="J34" s="24" t="n">
-        <v>15247</v>
+        <v>51603</v>
       </c>
       <c r="K34" s="25" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="L34" s="25" t="n">
-        <v>1073</v>
+        <v>2832</v>
       </c>
       <c r="M34" s="26" t="n">
-        <v>5.8</v>
+        <v>1</v>
       </c>
       <c r="N34" s="26" t="n">
-        <v>1086</v>
+        <v>573</v>
       </c>
       <c r="O34" s="27" t="n">
-        <v>93.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="P34" s="27" t="n">
-        <v>17406</v>
+        <v>55009</v>
       </c>
       <c r="Q34" s="28" t="inlineStr">
         <is>
@@ -2691,41 +2595,41 @@
       <c r="D35" s="21" t="n"/>
       <c r="E35" s="22" t="inlineStr">
         <is>
-          <t>SO2604</t>
+          <t>SO2102</t>
         </is>
       </c>
       <c r="F35" s="22" t="n">
-        <v>9849</v>
+        <v>11470</v>
       </c>
       <c r="G35" s="23" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="H35" s="23" t="n">
-        <v>909</v>
+        <v>0</v>
       </c>
       <c r="I35" s="24" t="n">
-        <v>77.3</v>
+        <v>100</v>
       </c>
       <c r="J35" s="24" t="n">
-        <v>7612</v>
+        <v>11470</v>
       </c>
       <c r="K35" s="25" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L35" s="25" t="n">
-        <v>1186</v>
+        <v>0</v>
       </c>
       <c r="M35" s="26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N35" s="26" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="O35" s="27" t="n">
-        <v>90.8</v>
+        <v>100</v>
       </c>
       <c r="P35" s="27" t="n">
-        <v>8940</v>
+        <v>11470</v>
       </c>
       <c r="Q35" s="28" t="inlineStr">
         <is>
@@ -2740,41 +2644,41 @@
       <c r="D36" s="21" t="n"/>
       <c r="E36" s="22" t="inlineStr">
         <is>
-          <t>SO2605</t>
+          <t>SO2103</t>
         </is>
       </c>
       <c r="F36" s="22" t="n">
-        <v>40378</v>
+        <v>55853</v>
       </c>
       <c r="G36" s="23" t="n">
-        <v>43.2</v>
+        <v>75.8</v>
       </c>
       <c r="H36" s="23" t="n">
-        <v>17463</v>
+        <v>42310</v>
       </c>
       <c r="I36" s="24" t="n">
-        <v>37.7</v>
+        <v>17.1</v>
       </c>
       <c r="J36" s="24" t="n">
-        <v>15230</v>
+        <v>9564</v>
       </c>
       <c r="K36" s="25" t="n">
-        <v>16.8</v>
+        <v>6.2</v>
       </c>
       <c r="L36" s="25" t="n">
-        <v>6789</v>
+        <v>3459</v>
       </c>
       <c r="M36" s="26" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="N36" s="26" t="n">
-        <v>897</v>
+        <v>474</v>
       </c>
       <c r="O36" s="27" t="n">
-        <v>56.8</v>
+        <v>24.2</v>
       </c>
       <c r="P36" s="27" t="n">
-        <v>22915</v>
+        <v>13498</v>
       </c>
       <c r="Q36" s="28" t="inlineStr">
         <is>
@@ -2787,47 +2691,1174 @@
       <c r="B37" s="21" t="n"/>
       <c r="C37" s="21" t="n"/>
       <c r="D37" s="21" t="n"/>
-      <c r="E37" s="29" t="inlineStr">
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>SO2104</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="n">
+        <v>638</v>
+      </c>
+      <c r="G37" s="23" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H37" s="23" t="n">
+        <v>125</v>
+      </c>
+      <c r="I37" s="24" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="J37" s="24" t="n">
+        <v>509</v>
+      </c>
+      <c r="K37" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N37" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="O37" s="27" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="P37" s="27" t="n">
+        <v>513</v>
+      </c>
+      <c r="Q37" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="21" t="n"/>
+      <c r="B38" s="21" t="n"/>
+      <c r="C38" s="21" t="n"/>
+      <c r="D38" s="21" t="n"/>
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>SO2203</t>
+        </is>
+      </c>
+      <c r="F38" s="22" t="n">
+        <v>247922</v>
+      </c>
+      <c r="G38" s="23" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="H38" s="23" t="n">
+        <v>77848</v>
+      </c>
+      <c r="I38" s="24" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="J38" s="24" t="n">
+        <v>169083</v>
+      </c>
+      <c r="K38" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L38" s="25" t="n">
+        <v>744</v>
+      </c>
+      <c r="M38" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="27" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="P38" s="27" t="n">
+        <v>169827</v>
+      </c>
+      <c r="Q38" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="21" t="n"/>
+      <c r="B39" s="21" t="n"/>
+      <c r="C39" s="21" t="n"/>
+      <c r="D39" s="21" t="n"/>
+      <c r="E39" s="22" t="inlineStr">
+        <is>
+          <t>SO2210</t>
+        </is>
+      </c>
+      <c r="F39" s="22" t="n">
+        <v>171981</v>
+      </c>
+      <c r="G39" s="23" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="H39" s="23" t="n">
+        <v>61569</v>
+      </c>
+      <c r="I39" s="24" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="J39" s="24" t="n">
+        <v>102845</v>
+      </c>
+      <c r="K39" s="25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L39" s="25" t="n">
+        <v>6363</v>
+      </c>
+      <c r="M39" s="26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N39" s="26" t="n">
+        <v>1204</v>
+      </c>
+      <c r="O39" s="27" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="P39" s="27" t="n">
+        <v>110412</v>
+      </c>
+      <c r="Q39" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="n"/>
+      <c r="B40" s="21" t="n"/>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="22" t="inlineStr">
+        <is>
+          <t>SO2301</t>
+        </is>
+      </c>
+      <c r="F40" s="22" t="n">
+        <v>60255</v>
+      </c>
+      <c r="G40" s="23" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="H40" s="23" t="n">
+        <v>36790</v>
+      </c>
+      <c r="I40" s="24" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="J40" s="24" t="n">
+        <v>23104</v>
+      </c>
+      <c r="K40" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L40" s="25" t="n">
+        <v>181</v>
+      </c>
+      <c r="M40" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N40" s="26" t="n">
+        <v>181</v>
+      </c>
+      <c r="O40" s="27" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="P40" s="27" t="n">
+        <v>23465</v>
+      </c>
+      <c r="Q40" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="n"/>
+      <c r="B41" s="21" t="n"/>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="22" t="inlineStr">
+        <is>
+          <t>SO2302</t>
+        </is>
+      </c>
+      <c r="F41" s="22" t="n">
+        <v>74165</v>
+      </c>
+      <c r="G41" s="23" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H41" s="23" t="n">
+        <v>10343</v>
+      </c>
+      <c r="I41" s="24" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="J41" s="24" t="n">
+        <v>62098</v>
+      </c>
+      <c r="K41" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L41" s="25" t="n">
+        <v>427</v>
+      </c>
+      <c r="M41" s="26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N41" s="26" t="n">
+        <v>1290</v>
+      </c>
+      <c r="O41" s="27" t="n">
+        <v>86</v>
+      </c>
+      <c r="P41" s="27" t="n">
+        <v>63816</v>
+      </c>
+      <c r="Q41" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="21" t="n"/>
+      <c r="B42" s="21" t="n"/>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="22" t="inlineStr">
+        <is>
+          <t>SO2303</t>
+        </is>
+      </c>
+      <c r="F42" s="22" t="n">
+        <v>13582</v>
+      </c>
+      <c r="G42" s="23" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="H42" s="23" t="n">
+        <v>11381</v>
+      </c>
+      <c r="I42" s="24" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="J42" s="24" t="n">
+        <v>2200</v>
+      </c>
+      <c r="K42" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="27" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="P42" s="27" t="n">
+        <v>2200</v>
+      </c>
+      <c r="Q42" s="28" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="21" t="n"/>
+      <c r="B43" s="21" t="n"/>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="22" t="inlineStr">
+        <is>
+          <t>SO2305</t>
+        </is>
+      </c>
+      <c r="F43" s="22" t="n">
+        <v>29215</v>
+      </c>
+      <c r="G43" s="23" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="H43" s="23" t="n">
+        <v>10547</v>
+      </c>
+      <c r="I43" s="24" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="J43" s="24" t="n">
+        <v>17704</v>
+      </c>
+      <c r="K43" s="25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L43" s="25" t="n">
+        <v>351</v>
+      </c>
+      <c r="M43" s="26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N43" s="26" t="n">
+        <v>614</v>
+      </c>
+      <c r="O43" s="27" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="P43" s="27" t="n">
+        <v>18669</v>
+      </c>
+      <c r="Q43" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="21" t="n"/>
+      <c r="B44" s="21" t="n"/>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="22" t="inlineStr">
+        <is>
+          <t>SO2307</t>
+        </is>
+      </c>
+      <c r="F44" s="22" t="n">
+        <v>42673</v>
+      </c>
+      <c r="G44" s="23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H44" s="23" t="n">
+        <v>7487</v>
+      </c>
+      <c r="I44" s="24" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="J44" s="24" t="n">
+        <v>34275</v>
+      </c>
+      <c r="K44" s="25" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L44" s="25" t="n">
+        <v>311</v>
+      </c>
+      <c r="M44" s="26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N44" s="26" t="n">
+        <v>556</v>
+      </c>
+      <c r="O44" s="27" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="P44" s="27" t="n">
+        <v>35143</v>
+      </c>
+      <c r="Q44" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="n"/>
+      <c r="B45" s="21" t="n"/>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="22" t="inlineStr">
+        <is>
+          <t>SO2401</t>
+        </is>
+      </c>
+      <c r="F45" s="22" t="n">
+        <v>176201</v>
+      </c>
+      <c r="G45" s="23" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="H45" s="23" t="n">
+        <v>62903</v>
+      </c>
+      <c r="I45" s="24" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="J45" s="24" t="n">
+        <v>104965</v>
+      </c>
+      <c r="K45" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L45" s="25" t="n">
+        <v>6144</v>
+      </c>
+      <c r="M45" s="26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N45" s="26" t="n">
+        <v>2188</v>
+      </c>
+      <c r="O45" s="27" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="P45" s="27" t="n">
+        <v>113298</v>
+      </c>
+      <c r="Q45" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="21" t="n"/>
+      <c r="B46" s="21" t="n"/>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="22" t="inlineStr">
+        <is>
+          <t>SO2402</t>
+        </is>
+      </c>
+      <c r="F46" s="22" t="n">
+        <v>39025</v>
+      </c>
+      <c r="G46" s="23" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="H46" s="23" t="n">
+        <v>10599</v>
+      </c>
+      <c r="I46" s="24" t="n">
+        <v>65</v>
+      </c>
+      <c r="J46" s="24" t="n">
+        <v>25380</v>
+      </c>
+      <c r="K46" s="25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L46" s="25" t="n">
+        <v>655</v>
+      </c>
+      <c r="M46" s="26" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="N46" s="26" t="n">
+        <v>2392</v>
+      </c>
+      <c r="O46" s="27" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="P46" s="27" t="n">
+        <v>28427</v>
+      </c>
+      <c r="Q46" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="21" t="n"/>
+      <c r="B47" s="21" t="n"/>
+      <c r="C47" s="21" t="n"/>
+      <c r="D47" s="21" t="n"/>
+      <c r="E47" s="22" t="inlineStr">
+        <is>
+          <t>SO2403</t>
+        </is>
+      </c>
+      <c r="F47" s="22" t="n">
+        <v>36097</v>
+      </c>
+      <c r="G47" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="H47" s="23" t="n">
+        <v>1811</v>
+      </c>
+      <c r="I47" s="24" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="J47" s="24" t="n">
+        <v>32462</v>
+      </c>
+      <c r="K47" s="25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L47" s="25" t="n">
+        <v>485</v>
+      </c>
+      <c r="M47" s="26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N47" s="26" t="n">
+        <v>1365</v>
+      </c>
+      <c r="O47" s="27" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="P47" s="27" t="n">
+        <v>34313</v>
+      </c>
+      <c r="Q47" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="21" t="n"/>
+      <c r="B48" s="21" t="n"/>
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="21" t="n"/>
+      <c r="E48" s="22" t="inlineStr">
+        <is>
+          <t>SO2404</t>
+        </is>
+      </c>
+      <c r="F48" s="22" t="n">
+        <v>30823</v>
+      </c>
+      <c r="G48" s="23" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="H48" s="23" t="n">
+        <v>14683</v>
+      </c>
+      <c r="I48" s="24" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="J48" s="24" t="n">
+        <v>14548</v>
+      </c>
+      <c r="K48" s="25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L48" s="25" t="n">
+        <v>382</v>
+      </c>
+      <c r="M48" s="26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N48" s="26" t="n">
+        <v>1205</v>
+      </c>
+      <c r="O48" s="27" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="P48" s="27" t="n">
+        <v>16134</v>
+      </c>
+      <c r="Q48" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="21" t="n"/>
+      <c r="B49" s="21" t="n"/>
+      <c r="C49" s="21" t="n"/>
+      <c r="D49" s="21" t="n"/>
+      <c r="E49" s="22" t="inlineStr">
+        <is>
+          <t>SO2501</t>
+        </is>
+      </c>
+      <c r="F49" s="22" t="n">
+        <v>16004</v>
+      </c>
+      <c r="G49" s="23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H49" s="23" t="n">
+        <v>1472</v>
+      </c>
+      <c r="I49" s="24" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="J49" s="24" t="n">
+        <v>13795</v>
+      </c>
+      <c r="K49" s="25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L49" s="25" t="n">
+        <v>144</v>
+      </c>
+      <c r="M49" s="26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N49" s="26" t="n">
+        <v>592</v>
+      </c>
+      <c r="O49" s="27" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="P49" s="27" t="n">
+        <v>14531</v>
+      </c>
+      <c r="Q49" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="21" t="n"/>
+      <c r="B50" s="21" t="n"/>
+      <c r="C50" s="21" t="n"/>
+      <c r="D50" s="21" t="n"/>
+      <c r="E50" s="22" t="inlineStr">
+        <is>
+          <t>SO2504</t>
+        </is>
+      </c>
+      <c r="F50" s="22" t="n">
+        <v>17438</v>
+      </c>
+      <c r="G50" s="23" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="H50" s="23" t="n">
+        <v>9498</v>
+      </c>
+      <c r="I50" s="24" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="J50" s="24" t="n">
+        <v>7940</v>
+      </c>
+      <c r="K50" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="27" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="P50" s="27" t="n">
+        <v>7940</v>
+      </c>
+      <c r="Q50" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="21" t="n"/>
+      <c r="B51" s="21" t="n"/>
+      <c r="C51" s="21" t="n"/>
+      <c r="D51" s="21" t="n"/>
+      <c r="E51" s="22" t="inlineStr">
+        <is>
+          <t>SO2601</t>
+        </is>
+      </c>
+      <c r="F51" s="22" t="n">
+        <v>18832</v>
+      </c>
+      <c r="G51" s="23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H51" s="23" t="n">
+        <v>779</v>
+      </c>
+      <c r="I51" s="24" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="J51" s="24" t="n">
+        <v>15098</v>
+      </c>
+      <c r="K51" s="25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="L51" s="25" t="n">
+        <v>2536</v>
+      </c>
+      <c r="M51" s="26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N51" s="26" t="n">
+        <v>419</v>
+      </c>
+      <c r="O51" s="27" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="P51" s="27" t="n">
+        <v>18053</v>
+      </c>
+      <c r="Q51" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="21" t="n"/>
+      <c r="B52" s="21" t="n"/>
+      <c r="C52" s="21" t="n"/>
+      <c r="D52" s="21" t="n"/>
+      <c r="E52" s="22" t="inlineStr">
+        <is>
+          <t>SO2602</t>
+        </is>
+      </c>
+      <c r="F52" s="22" t="n">
+        <v>37431</v>
+      </c>
+      <c r="G52" s="23" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="H52" s="23" t="n">
+        <v>13968</v>
+      </c>
+      <c r="I52" s="24" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="J52" s="24" t="n">
+        <v>21205</v>
+      </c>
+      <c r="K52" s="25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L52" s="25" t="n">
+        <v>1589</v>
+      </c>
+      <c r="M52" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N52" s="26" t="n">
+        <v>658</v>
+      </c>
+      <c r="O52" s="27" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="P52" s="27" t="n">
+        <v>23452</v>
+      </c>
+      <c r="Q52" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="21" t="n"/>
+      <c r="B53" s="21" t="n"/>
+      <c r="C53" s="21" t="n"/>
+      <c r="D53" s="21" t="n"/>
+      <c r="E53" s="22" t="inlineStr">
+        <is>
+          <t>SO2603</t>
+        </is>
+      </c>
+      <c r="F53" s="22" t="n">
+        <v>18703</v>
+      </c>
+      <c r="G53" s="23" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H53" s="23" t="n">
+        <v>1297</v>
+      </c>
+      <c r="I53" s="24" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="J53" s="24" t="n">
+        <v>15247</v>
+      </c>
+      <c r="K53" s="25" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L53" s="25" t="n">
+        <v>1073</v>
+      </c>
+      <c r="M53" s="26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N53" s="26" t="n">
+        <v>1086</v>
+      </c>
+      <c r="O53" s="27" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="P53" s="27" t="n">
+        <v>17406</v>
+      </c>
+      <c r="Q53" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="21" t="n"/>
+      <c r="B54" s="21" t="n"/>
+      <c r="C54" s="21" t="n"/>
+      <c r="D54" s="21" t="n"/>
+      <c r="E54" s="22" t="inlineStr">
+        <is>
+          <t>SO2604</t>
+        </is>
+      </c>
+      <c r="F54" s="22" t="n">
+        <v>9849</v>
+      </c>
+      <c r="G54" s="23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H54" s="23" t="n">
+        <v>909</v>
+      </c>
+      <c r="I54" s="24" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="J54" s="24" t="n">
+        <v>7612</v>
+      </c>
+      <c r="K54" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="L54" s="25" t="n">
+        <v>1186</v>
+      </c>
+      <c r="M54" s="26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N54" s="26" t="n">
+        <v>143</v>
+      </c>
+      <c r="O54" s="27" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="P54" s="27" t="n">
+        <v>8940</v>
+      </c>
+      <c r="Q54" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="21" t="n"/>
+      <c r="B55" s="21" t="n"/>
+      <c r="C55" s="21" t="n"/>
+      <c r="D55" s="21" t="n"/>
+      <c r="E55" s="22" t="inlineStr">
+        <is>
+          <t>SO2605</t>
+        </is>
+      </c>
+      <c r="F55" s="22" t="n">
+        <v>40378</v>
+      </c>
+      <c r="G55" s="23" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="H55" s="23" t="n">
+        <v>17463</v>
+      </c>
+      <c r="I55" s="24" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J55" s="24" t="n">
+        <v>15230</v>
+      </c>
+      <c r="K55" s="25" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="L55" s="25" t="n">
+        <v>6789</v>
+      </c>
+      <c r="M55" s="26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N55" s="26" t="n">
+        <v>897</v>
+      </c>
+      <c r="O55" s="27" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="P55" s="27" t="n">
+        <v>22915</v>
+      </c>
+      <c r="Q55" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="21" t="n"/>
+      <c r="B56" s="21" t="n"/>
+      <c r="C56" s="21" t="n"/>
+      <c r="D56" s="21" t="n"/>
+      <c r="E56" s="22" t="inlineStr">
         <is>
           <t>SO2606</t>
         </is>
       </c>
-      <c r="F37" s="29" t="n">
+      <c r="F56" s="22" t="n">
         <v>23742</v>
       </c>
-      <c r="G37" s="30" t="n">
+      <c r="G56" s="23" t="n">
         <v>18.2</v>
       </c>
-      <c r="H37" s="30" t="n">
+      <c r="H56" s="23" t="n">
         <v>4324</v>
       </c>
-      <c r="I37" s="31" t="n">
+      <c r="I56" s="24" t="n">
         <v>80</v>
       </c>
-      <c r="J37" s="31" t="n">
+      <c r="J56" s="24" t="n">
         <v>18985</v>
       </c>
-      <c r="K37" s="32" t="n">
+      <c r="K56" s="25" t="n">
         <v>1.8</v>
       </c>
-      <c r="L37" s="32" t="n">
+      <c r="L56" s="25" t="n">
         <v>438</v>
       </c>
-      <c r="M37" s="33" t="n">
+      <c r="M56" s="26" t="n">
         <v>0.1</v>
       </c>
-      <c r="N37" s="33" t="n">
+      <c r="N56" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="O37" s="34" t="n">
+      <c r="O56" s="27" t="n">
         <v>81.90000000000001</v>
       </c>
-      <c r="P37" s="34" t="n">
+      <c r="P56" s="27" t="n">
         <v>19438</v>
       </c>
-      <c r="Q37" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="Q56" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="21" t="n"/>
+      <c r="B57" s="21" t="n"/>
+      <c r="C57" s="21" t="n"/>
+      <c r="D57" s="21" t="n"/>
+      <c r="E57" s="22" t="inlineStr">
+        <is>
+          <t>SO2801</t>
+        </is>
+      </c>
+      <c r="F57" s="22" t="n">
+        <v>44224</v>
+      </c>
+      <c r="G57" s="23" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="H57" s="23" t="n">
+        <v>21093</v>
+      </c>
+      <c r="I57" s="24" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="J57" s="24" t="n">
+        <v>14279</v>
+      </c>
+      <c r="K57" s="25" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="L57" s="25" t="n">
+        <v>6445</v>
+      </c>
+      <c r="M57" s="26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N57" s="26" t="n">
+        <v>2414</v>
+      </c>
+      <c r="O57" s="27" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="P57" s="27" t="n">
+        <v>23138</v>
+      </c>
+      <c r="Q57" s="28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="21" t="n"/>
+      <c r="B58" s="21" t="n"/>
+      <c r="C58" s="21" t="n"/>
+      <c r="D58" s="21" t="n"/>
+      <c r="E58" s="22" t="inlineStr">
+        <is>
+          <t>SO2802</t>
+        </is>
+      </c>
+      <c r="F58" s="22" t="n">
+        <v>57479</v>
+      </c>
+      <c r="G58" s="23" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="H58" s="23" t="n">
+        <v>45291</v>
+      </c>
+      <c r="I58" s="24" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J58" s="24" t="n">
+        <v>9604</v>
+      </c>
+      <c r="K58" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="L58" s="25" t="n">
+        <v>2310</v>
+      </c>
+      <c r="M58" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N58" s="26" t="n">
+        <v>273</v>
+      </c>
+      <c r="O58" s="27" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="P58" s="27" t="n">
+        <v>12187</v>
+      </c>
+      <c r="Q58" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="21" t="n"/>
+      <c r="B59" s="21" t="n"/>
+      <c r="C59" s="21" t="n"/>
+      <c r="D59" s="21" t="n"/>
+      <c r="E59" s="22" t="inlineStr">
+        <is>
+          <t>SO2803</t>
+        </is>
+      </c>
+      <c r="F59" s="22" t="n">
+        <v>7176</v>
+      </c>
+      <c r="G59" s="23" t="n">
+        <v>55</v>
+      </c>
+      <c r="H59" s="23" t="n">
+        <v>3947</v>
+      </c>
+      <c r="I59" s="24" t="n">
+        <v>40</v>
+      </c>
+      <c r="J59" s="24" t="n">
+        <v>2870</v>
+      </c>
+      <c r="K59" s="25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L59" s="25" t="n">
+        <v>237</v>
+      </c>
+      <c r="M59" s="26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N59" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="O59" s="27" t="n">
+        <v>45</v>
+      </c>
+      <c r="P59" s="27" t="n">
+        <v>3229</v>
+      </c>
+      <c r="Q59" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="21" t="n"/>
+      <c r="B60" s="21" t="n"/>
+      <c r="C60" s="21" t="n"/>
+      <c r="D60" s="21" t="n"/>
+      <c r="E60" s="29" t="inlineStr">
+        <is>
+          <t>SO2804</t>
+        </is>
+      </c>
+      <c r="F60" s="29" t="n">
+        <v>47753</v>
+      </c>
+      <c r="G60" s="30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H60" s="30" t="n">
+        <v>1146</v>
+      </c>
+      <c r="I60" s="31" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="J60" s="31" t="n">
+        <v>31469</v>
+      </c>
+      <c r="K60" s="32" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L60" s="32" t="n">
+        <v>9312</v>
+      </c>
+      <c r="M60" s="33" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="N60" s="33" t="n">
+        <v>5826</v>
+      </c>
+      <c r="O60" s="34" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="P60" s="34" t="n">
+        <v>46607</v>
+      </c>
+      <c r="Q60" s="28" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2845,7 +3876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W37"/>
+  <dimension ref="A1:R60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="5" max="5"/>
@@ -2862,11 +3893,6 @@
     <col width="33" customWidth="1" min="16" max="16"/>
     <col width="33" customWidth="1" min="17" max="17"/>
     <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="47" customWidth="1" min="20" max="20"/>
-    <col width="44" customWidth="1" min="21" max="21"/>
-    <col width="44" customWidth="1" min="22" max="22"/>
-    <col width="44" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2954,31 +3980,6 @@
           <t>Area severity</t>
         </is>
       </c>
-      <c r="S5" s="15" t="inlineStr">
-        <is>
-          <t>Admin_Pcode_2024</t>
-        </is>
-      </c>
-      <c r="T5" s="15" t="inlineStr">
-        <is>
-          <t>%_severity_levels_1-2_2024_extrapolation_base</t>
-        </is>
-      </c>
-      <c r="U5" s="15" t="inlineStr">
-        <is>
-          <t>%_severity_level_3_2024_extrapolation_base</t>
-        </is>
-      </c>
-      <c r="V5" s="15" t="inlineStr">
-        <is>
-          <t>%_severity_level_4_2024_extrapolation_base</t>
-        </is>
-      </c>
-      <c r="W5" s="15" t="inlineStr">
-        <is>
-          <t>%_severity_level_5_2024_extrapolation_base</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="21" t="n"/>
@@ -2987,7 +3988,7 @@
       <c r="D6" s="21" t="n"/>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>SO1103</t>
+          <t>SO1101</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -2996,48 +3997,43 @@
         </is>
       </c>
       <c r="G6" s="22" t="n">
-        <v>17071</v>
+        <v>123388</v>
       </c>
       <c r="H6" s="23" t="n">
-        <v>40.8</v>
+        <v>60.1</v>
       </c>
       <c r="I6" s="23" t="n">
-        <v>6965</v>
+        <v>74156</v>
       </c>
       <c r="J6" s="24" t="n">
-        <v>53.5</v>
+        <v>35.5</v>
       </c>
       <c r="K6" s="24" t="n">
-        <v>9133</v>
+        <v>43803</v>
       </c>
       <c r="L6" s="25" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="M6" s="25" t="n">
-        <v>717</v>
+        <v>5429</v>
       </c>
       <c r="N6" s="26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O6" s="26" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="P6" s="27" t="n">
-        <v>59.1</v>
+        <v>39.9</v>
       </c>
       <c r="Q6" s="27" t="n">
-        <v>10089</v>
-      </c>
-      <c r="R6" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S6" s="22" t="inlineStr"/>
-      <c r="T6" s="22" t="inlineStr"/>
-      <c r="U6" s="22" t="inlineStr"/>
-      <c r="V6" s="22" t="inlineStr"/>
-      <c r="W6" s="35" t="inlineStr"/>
+        <v>49232</v>
+      </c>
+      <c r="R6" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="21" t="n"/>
@@ -3046,7 +4042,7 @@
       <c r="D7" s="21" t="n"/>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>SO1104</t>
+          <t>SO1102</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -3055,25 +4051,25 @@
         </is>
       </c>
       <c r="G7" s="22" t="n">
-        <v>15492</v>
+        <v>11059</v>
       </c>
       <c r="H7" s="23" t="n">
-        <v>37.8</v>
+        <v>64.5</v>
       </c>
       <c r="I7" s="23" t="n">
-        <v>5856</v>
+        <v>7133</v>
       </c>
       <c r="J7" s="24" t="n">
-        <v>55.2</v>
+        <v>33.2</v>
       </c>
       <c r="K7" s="24" t="n">
-        <v>8552</v>
+        <v>3672</v>
       </c>
       <c r="L7" s="25" t="n">
-        <v>7</v>
+        <v>2.4</v>
       </c>
       <c r="M7" s="25" t="n">
-        <v>1084</v>
+        <v>265</v>
       </c>
       <c r="N7" s="26" t="n">
         <v>0</v>
@@ -3082,21 +4078,16 @@
         <v>0</v>
       </c>
       <c r="P7" s="27" t="n">
-        <v>62.2</v>
+        <v>35.6</v>
       </c>
       <c r="Q7" s="27" t="n">
-        <v>9636</v>
-      </c>
-      <c r="R7" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S7" s="22" t="inlineStr"/>
-      <c r="T7" s="22" t="inlineStr"/>
-      <c r="U7" s="22" t="inlineStr"/>
-      <c r="V7" s="22" t="inlineStr"/>
-      <c r="W7" s="35" t="inlineStr"/>
+        <v>3937</v>
+      </c>
+      <c r="R7" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="21" t="n"/>
@@ -3105,7 +4096,7 @@
       <c r="D8" s="21" t="n"/>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>SO1202</t>
+          <t>SO1201</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -3114,48 +4105,43 @@
         </is>
       </c>
       <c r="G8" s="22" t="n">
-        <v>36044</v>
+        <v>187972</v>
       </c>
       <c r="H8" s="23" t="n">
-        <v>82.8</v>
+        <v>37.1</v>
       </c>
       <c r="I8" s="23" t="n">
-        <v>29845</v>
+        <v>69738</v>
       </c>
       <c r="J8" s="24" t="n">
-        <v>15.7</v>
+        <v>54.8</v>
       </c>
       <c r="K8" s="24" t="n">
-        <v>5659</v>
+        <v>103009</v>
       </c>
       <c r="L8" s="25" t="n">
-        <v>1.2</v>
+        <v>8.1</v>
       </c>
       <c r="M8" s="25" t="n">
-        <v>433</v>
+        <v>15226</v>
       </c>
       <c r="N8" s="26" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="O8" s="26" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="P8" s="27" t="n">
-        <v>17.2</v>
+        <v>62.9</v>
       </c>
       <c r="Q8" s="27" t="n">
-        <v>6200</v>
-      </c>
-      <c r="R8" s="27" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="S8" s="22" t="inlineStr"/>
-      <c r="T8" s="22" t="inlineStr"/>
-      <c r="U8" s="22" t="inlineStr"/>
-      <c r="V8" s="22" t="inlineStr"/>
-      <c r="W8" s="35" t="inlineStr"/>
+        <v>118234</v>
+      </c>
+      <c r="R8" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="21" t="n"/>
@@ -3164,7 +4150,7 @@
       <c r="D9" s="21" t="n"/>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>SO1304</t>
+          <t>SO1401</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -3173,25 +4159,25 @@
         </is>
       </c>
       <c r="G9" s="22" t="n">
-        <v>23365</v>
+        <v>50361</v>
       </c>
       <c r="H9" s="23" t="n">
-        <v>42.9</v>
+        <v>22.2</v>
       </c>
       <c r="I9" s="23" t="n">
-        <v>10024</v>
+        <v>11180</v>
       </c>
       <c r="J9" s="24" t="n">
-        <v>47.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>11028</v>
+        <v>37821</v>
       </c>
       <c r="L9" s="25" t="n">
-        <v>9.800000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="M9" s="25" t="n">
-        <v>2290</v>
+        <v>1360</v>
       </c>
       <c r="N9" s="26" t="n">
         <v>0</v>
@@ -3200,21 +4186,16 @@
         <v>0</v>
       </c>
       <c r="P9" s="27" t="n">
-        <v>57</v>
+        <v>77.8</v>
       </c>
       <c r="Q9" s="27" t="n">
-        <v>13318</v>
-      </c>
-      <c r="R9" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S9" s="22" t="inlineStr"/>
-      <c r="T9" s="22" t="inlineStr"/>
-      <c r="U9" s="22" t="inlineStr"/>
-      <c r="V9" s="22" t="inlineStr"/>
-      <c r="W9" s="35" t="inlineStr"/>
+        <v>39181</v>
+      </c>
+      <c r="R9" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="21" t="n"/>
@@ -3223,7 +4204,7 @@
       <c r="D10" s="21" t="n"/>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>SO1501</t>
+          <t>SO1502</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -3232,48 +4213,43 @@
         </is>
       </c>
       <c r="G10" s="22" t="n">
-        <v>31394</v>
+        <v>19315</v>
       </c>
       <c r="H10" s="23" t="n">
-        <v>41.8</v>
+        <v>62.2</v>
       </c>
       <c r="I10" s="23" t="n">
-        <v>13123</v>
+        <v>12014</v>
       </c>
       <c r="J10" s="24" t="n">
-        <v>55.3</v>
+        <v>37.1</v>
       </c>
       <c r="K10" s="24" t="n">
-        <v>17361</v>
+        <v>7166</v>
       </c>
       <c r="L10" s="25" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="M10" s="25" t="n">
-        <v>659</v>
+        <v>58</v>
       </c>
       <c r="N10" s="26" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="O10" s="26" t="n">
-        <v>251</v>
+        <v>58</v>
       </c>
       <c r="P10" s="27" t="n">
-        <v>58.2</v>
+        <v>37.7</v>
       </c>
       <c r="Q10" s="27" t="n">
-        <v>18271</v>
-      </c>
-      <c r="R10" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S10" s="22" t="inlineStr"/>
-      <c r="T10" s="22" t="inlineStr"/>
-      <c r="U10" s="22" t="inlineStr"/>
-      <c r="V10" s="22" t="inlineStr"/>
-      <c r="W10" s="35" t="inlineStr"/>
+        <v>7282</v>
+      </c>
+      <c r="R10" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="21" t="n"/>
@@ -3282,7 +4258,7 @@
       <c r="D11" s="21" t="n"/>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>SO1503</t>
+          <t>SO1601</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -3291,48 +4267,43 @@
         </is>
       </c>
       <c r="G11" s="22" t="n">
-        <v>32784</v>
+        <v>142297</v>
       </c>
       <c r="H11" s="23" t="n">
-        <v>25.4</v>
+        <v>34.6</v>
       </c>
       <c r="I11" s="23" t="n">
-        <v>8327</v>
+        <v>49235</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>73.09999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>23965</v>
+        <v>92208</v>
       </c>
       <c r="L11" s="25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M11" s="25" t="n">
-        <v>525</v>
+        <v>0</v>
       </c>
       <c r="N11" s="26" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="O11" s="26" t="n">
-        <v>0</v>
+        <v>854</v>
       </c>
       <c r="P11" s="27" t="n">
-        <v>74.7</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="Q11" s="27" t="n">
-        <v>24490</v>
-      </c>
-      <c r="R11" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S11" s="22" t="inlineStr"/>
-      <c r="T11" s="22" t="inlineStr"/>
-      <c r="U11" s="22" t="inlineStr"/>
-      <c r="V11" s="22" t="inlineStr"/>
-      <c r="W11" s="35" t="inlineStr"/>
+        <v>93062</v>
+      </c>
+      <c r="R11" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="21" t="n"/>
@@ -3341,7 +4312,7 @@
       <c r="D12" s="21" t="n"/>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>SO1604</t>
+          <t>SO1602</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -3350,48 +4321,43 @@
         </is>
       </c>
       <c r="G12" s="22" t="n">
-        <v>9184</v>
+        <v>9550</v>
       </c>
       <c r="H12" s="23" t="n">
-        <v>44</v>
+        <v>45.5</v>
       </c>
       <c r="I12" s="23" t="n">
-        <v>4041</v>
+        <v>4345</v>
       </c>
       <c r="J12" s="24" t="n">
-        <v>48.2</v>
+        <v>54</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>4427</v>
+        <v>5157</v>
       </c>
       <c r="L12" s="25" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="M12" s="25" t="n">
-        <v>716</v>
+        <v>0</v>
       </c>
       <c r="N12" s="26" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O12" s="26" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="P12" s="27" t="n">
-        <v>56</v>
+        <v>54.5</v>
       </c>
       <c r="Q12" s="27" t="n">
-        <v>5143</v>
-      </c>
-      <c r="R12" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S12" s="22" t="inlineStr"/>
-      <c r="T12" s="22" t="inlineStr"/>
-      <c r="U12" s="22" t="inlineStr"/>
-      <c r="V12" s="22" t="inlineStr"/>
-      <c r="W12" s="35" t="inlineStr"/>
+        <v>5205</v>
+      </c>
+      <c r="R12" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="21" t="n"/>
@@ -3400,7 +4366,7 @@
       <c r="D13" s="21" t="n"/>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t>SO1701</t>
+          <t>SO1603</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -3409,48 +4375,43 @@
         </is>
       </c>
       <c r="G13" s="22" t="n">
-        <v>61170</v>
+        <v>17619</v>
       </c>
       <c r="H13" s="23" t="n">
-        <v>53.7</v>
+        <v>42.4</v>
       </c>
       <c r="I13" s="23" t="n">
-        <v>32848</v>
+        <v>7471</v>
       </c>
       <c r="J13" s="24" t="n">
-        <v>45.3</v>
+        <v>55.3</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>27710</v>
+        <v>9743</v>
       </c>
       <c r="L13" s="25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M13" s="25" t="n">
-        <v>0</v>
+        <v>405</v>
       </c>
       <c r="N13" s="26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" s="26" t="n">
-        <v>612</v>
+        <v>0</v>
       </c>
       <c r="P13" s="27" t="n">
-        <v>46.3</v>
+        <v>57.6</v>
       </c>
       <c r="Q13" s="27" t="n">
-        <v>28322</v>
-      </c>
-      <c r="R13" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S13" s="22" t="inlineStr"/>
-      <c r="T13" s="22" t="inlineStr"/>
-      <c r="U13" s="22" t="inlineStr"/>
-      <c r="V13" s="22" t="inlineStr"/>
-      <c r="W13" s="35" t="inlineStr"/>
+        <v>10149</v>
+      </c>
+      <c r="R13" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="21" t="n"/>
@@ -3459,7 +4420,7 @@
       <c r="D14" s="21" t="n"/>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>SO1801</t>
+          <t>SO1606</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -3468,48 +4429,43 @@
         </is>
       </c>
       <c r="G14" s="22" t="n">
-        <v>182675</v>
+        <v>28857</v>
       </c>
       <c r="H14" s="23" t="n">
-        <v>50.6</v>
+        <v>34</v>
       </c>
       <c r="I14" s="23" t="n">
-        <v>92433</v>
+        <v>9811</v>
       </c>
       <c r="J14" s="24" t="n">
-        <v>41.1</v>
+        <v>62.9</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>75079</v>
+        <v>18151</v>
       </c>
       <c r="L14" s="25" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="M14" s="25" t="n">
-        <v>6028</v>
+        <v>548</v>
       </c>
       <c r="N14" s="26" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="O14" s="26" t="n">
-        <v>9134</v>
+        <v>375</v>
       </c>
       <c r="P14" s="27" t="n">
-        <v>49.4</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="Q14" s="27" t="n">
-        <v>90241</v>
-      </c>
-      <c r="R14" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S14" s="22" t="inlineStr"/>
-      <c r="T14" s="22" t="inlineStr"/>
-      <c r="U14" s="22" t="inlineStr"/>
-      <c r="V14" s="22" t="inlineStr"/>
-      <c r="W14" s="35" t="inlineStr"/>
+        <v>19074</v>
+      </c>
+      <c r="R14" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="21" t="n"/>
@@ -3518,7 +4474,7 @@
       <c r="D15" s="21" t="n"/>
       <c r="E15" s="22" t="inlineStr">
         <is>
-          <t>SO1802</t>
+          <t>SO1702</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -3527,48 +4483,43 @@
         </is>
       </c>
       <c r="G15" s="22" t="n">
-        <v>35703</v>
+        <v>24113</v>
       </c>
       <c r="H15" s="23" t="n">
-        <v>70.59999999999999</v>
+        <v>29.5</v>
       </c>
       <c r="I15" s="23" t="n">
-        <v>25206</v>
+        <v>7113</v>
       </c>
       <c r="J15" s="24" t="n">
-        <v>28.4</v>
+        <v>70.2</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>10140</v>
+        <v>16927</v>
       </c>
       <c r="L15" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="25" t="n">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="N15" s="26" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O15" s="26" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="P15" s="27" t="n">
-        <v>29.4</v>
+        <v>70.5</v>
       </c>
       <c r="Q15" s="27" t="n">
-        <v>10497</v>
-      </c>
-      <c r="R15" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S15" s="22" t="inlineStr"/>
-      <c r="T15" s="22" t="inlineStr"/>
-      <c r="U15" s="22" t="inlineStr"/>
-      <c r="V15" s="22" t="inlineStr"/>
-      <c r="W15" s="35" t="inlineStr"/>
+        <v>17000</v>
+      </c>
+      <c r="R15" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="21" t="n"/>
@@ -3577,7 +4528,7 @@
       <c r="D16" s="21" t="n"/>
       <c r="E16" s="22" t="inlineStr">
         <is>
-          <t>SO1803</t>
+          <t>SO1804</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -3586,25 +4537,25 @@
         </is>
       </c>
       <c r="G16" s="22" t="n">
-        <v>46864</v>
+        <v>44874</v>
       </c>
       <c r="H16" s="23" t="n">
-        <v>35.3</v>
+        <v>38.3</v>
       </c>
       <c r="I16" s="23" t="n">
-        <v>16543</v>
+        <v>17187</v>
       </c>
       <c r="J16" s="24" t="n">
-        <v>62.9</v>
+        <v>54.7</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>29477</v>
+        <v>24546</v>
       </c>
       <c r="L16" s="25" t="n">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="M16" s="25" t="n">
-        <v>844</v>
+        <v>3141</v>
       </c>
       <c r="N16" s="26" t="n">
         <v>0</v>
@@ -3613,21 +4564,16 @@
         <v>0</v>
       </c>
       <c r="P16" s="27" t="n">
-        <v>64.7</v>
+        <v>61.7</v>
       </c>
       <c r="Q16" s="27" t="n">
-        <v>30321</v>
-      </c>
-      <c r="R16" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S16" s="22" t="inlineStr"/>
-      <c r="T16" s="22" t="inlineStr"/>
-      <c r="U16" s="22" t="inlineStr"/>
-      <c r="V16" s="22" t="inlineStr"/>
-      <c r="W16" s="35" t="inlineStr"/>
+        <v>27687</v>
+      </c>
+      <c r="R16" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="21" t="n"/>
@@ -3636,7 +4582,7 @@
       <c r="D17" s="21" t="n"/>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>SO1901</t>
+          <t>SO2102</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -3645,25 +4591,25 @@
         </is>
       </c>
       <c r="G17" s="22" t="n">
-        <v>64063</v>
+        <v>11470</v>
       </c>
       <c r="H17" s="23" t="n">
-        <v>25.2</v>
+        <v>0</v>
       </c>
       <c r="I17" s="23" t="n">
-        <v>16144</v>
+        <v>0</v>
       </c>
       <c r="J17" s="24" t="n">
-        <v>60.1</v>
+        <v>100</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>38502</v>
+        <v>11470</v>
       </c>
       <c r="L17" s="25" t="n">
-        <v>14.7</v>
+        <v>0</v>
       </c>
       <c r="M17" s="25" t="n">
-        <v>9417</v>
+        <v>0</v>
       </c>
       <c r="N17" s="26" t="n">
         <v>0</v>
@@ -3672,21 +4618,16 @@
         <v>0</v>
       </c>
       <c r="P17" s="27" t="n">
-        <v>74.8</v>
+        <v>100</v>
       </c>
       <c r="Q17" s="27" t="n">
-        <v>47919</v>
-      </c>
-      <c r="R17" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S17" s="22" t="inlineStr"/>
-      <c r="T17" s="22" t="inlineStr"/>
-      <c r="U17" s="22" t="inlineStr"/>
-      <c r="V17" s="22" t="inlineStr"/>
-      <c r="W17" s="35" t="inlineStr"/>
+        <v>11470</v>
+      </c>
+      <c r="R17" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="21" t="n"/>
@@ -3695,7 +4636,7 @@
       <c r="D18" s="21" t="n"/>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>SO1902</t>
+          <t>SO2103</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -3704,48 +4645,43 @@
         </is>
       </c>
       <c r="G18" s="22" t="n">
-        <v>50364</v>
+        <v>45310</v>
       </c>
       <c r="H18" s="23" t="n">
-        <v>45.8</v>
+        <v>85.7</v>
       </c>
       <c r="I18" s="23" t="n">
-        <v>23067</v>
+        <v>38830</v>
       </c>
       <c r="J18" s="24" t="n">
-        <v>51.8</v>
+        <v>7.1</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>26088</v>
+        <v>3217</v>
       </c>
       <c r="L18" s="25" t="n">
-        <v>2.1</v>
+        <v>7.1</v>
       </c>
       <c r="M18" s="25" t="n">
-        <v>1058</v>
+        <v>3217</v>
       </c>
       <c r="N18" s="26" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O18" s="26" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="P18" s="27" t="n">
-        <v>54.3</v>
+        <v>14.2</v>
       </c>
       <c r="Q18" s="27" t="n">
-        <v>27348</v>
-      </c>
-      <c r="R18" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S18" s="22" t="inlineStr"/>
-      <c r="T18" s="22" t="inlineStr"/>
-      <c r="U18" s="22" t="inlineStr"/>
-      <c r="V18" s="22" t="inlineStr"/>
-      <c r="W18" s="35" t="inlineStr"/>
+        <v>6434</v>
+      </c>
+      <c r="R18" s="28" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="21" t="n"/>
@@ -3754,7 +4690,7 @@
       <c r="D19" s="21" t="n"/>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>SO1903</t>
+          <t>SO2104</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -3763,48 +4699,43 @@
         </is>
       </c>
       <c r="G19" s="22" t="n">
-        <v>34105</v>
+        <v>638</v>
       </c>
       <c r="H19" s="23" t="n">
-        <v>35.9</v>
+        <v>19.6</v>
       </c>
       <c r="I19" s="23" t="n">
-        <v>12244</v>
+        <v>125</v>
       </c>
       <c r="J19" s="24" t="n">
-        <v>62.3</v>
+        <v>79.7</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>21248</v>
+        <v>509</v>
       </c>
       <c r="L19" s="25" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M19" s="25" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="N19" s="26" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="O19" s="26" t="n">
-        <v>477</v>
+        <v>4</v>
       </c>
       <c r="P19" s="27" t="n">
-        <v>64.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="Q19" s="27" t="n">
-        <v>21896</v>
-      </c>
-      <c r="R19" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S19" s="22" t="inlineStr"/>
-      <c r="T19" s="22" t="inlineStr"/>
-      <c r="U19" s="22" t="inlineStr"/>
-      <c r="V19" s="22" t="inlineStr"/>
-      <c r="W19" s="35" t="inlineStr"/>
+        <v>513</v>
+      </c>
+      <c r="R19" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="21" t="n"/>
@@ -3813,7 +4744,7 @@
       <c r="D20" s="21" t="n"/>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>SO2001</t>
+          <t>SO2303</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -3822,48 +4753,43 @@
         </is>
       </c>
       <c r="G20" s="22" t="n">
-        <v>48711</v>
+        <v>13582</v>
       </c>
       <c r="H20" s="23" t="n">
-        <v>35.3</v>
+        <v>83.8</v>
       </c>
       <c r="I20" s="23" t="n">
-        <v>17195</v>
+        <v>11381</v>
       </c>
       <c r="J20" s="24" t="n">
-        <v>62.6</v>
+        <v>16.2</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>30493</v>
+        <v>2200</v>
       </c>
       <c r="L20" s="25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M20" s="25" t="n">
-        <v>877</v>
+        <v>0</v>
       </c>
       <c r="N20" s="26" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="O20" s="26" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="P20" s="27" t="n">
-        <v>64.7</v>
+        <v>16.2</v>
       </c>
       <c r="Q20" s="27" t="n">
-        <v>31516</v>
-      </c>
-      <c r="R20" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S20" s="22" t="inlineStr"/>
-      <c r="T20" s="22" t="inlineStr"/>
-      <c r="U20" s="22" t="inlineStr"/>
-      <c r="V20" s="22" t="inlineStr"/>
-      <c r="W20" s="35" t="inlineStr"/>
+        <v>2200</v>
+      </c>
+      <c r="R20" s="28" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="21" t="n"/>
@@ -3872,7 +4798,7 @@
       <c r="D21" s="21" t="n"/>
       <c r="E21" s="22" t="inlineStr">
         <is>
-          <t>SO2002</t>
+          <t>SO2305</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -3881,48 +4807,43 @@
         </is>
       </c>
       <c r="G21" s="22" t="n">
-        <v>11508</v>
+        <v>29215</v>
       </c>
       <c r="H21" s="23" t="n">
-        <v>4.2</v>
+        <v>36.1</v>
       </c>
       <c r="I21" s="23" t="n">
-        <v>483</v>
+        <v>10547</v>
       </c>
       <c r="J21" s="24" t="n">
-        <v>83.3</v>
+        <v>60.6</v>
       </c>
       <c r="K21" s="24" t="n">
-        <v>9586</v>
+        <v>17704</v>
       </c>
       <c r="L21" s="25" t="n">
-        <v>10.6</v>
+        <v>1.2</v>
       </c>
       <c r="M21" s="25" t="n">
-        <v>1220</v>
+        <v>351</v>
       </c>
       <c r="N21" s="26" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="O21" s="26" t="n">
-        <v>219</v>
+        <v>614</v>
       </c>
       <c r="P21" s="27" t="n">
-        <v>95.8</v>
+        <v>63.9</v>
       </c>
       <c r="Q21" s="27" t="n">
-        <v>11025</v>
-      </c>
-      <c r="R21" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S21" s="22" t="inlineStr"/>
-      <c r="T21" s="22" t="inlineStr"/>
-      <c r="U21" s="22" t="inlineStr"/>
-      <c r="V21" s="22" t="inlineStr"/>
-      <c r="W21" s="35" t="inlineStr"/>
+        <v>18669</v>
+      </c>
+      <c r="R21" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="21" t="n"/>
@@ -3931,7 +4852,7 @@
       <c r="D22" s="21" t="n"/>
       <c r="E22" s="22" t="inlineStr">
         <is>
-          <t>SO2003</t>
+          <t>SO2307</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -3940,48 +4861,43 @@
         </is>
       </c>
       <c r="G22" s="22" t="n">
-        <v>10539</v>
+        <v>42481</v>
       </c>
       <c r="H22" s="23" t="n">
-        <v>46.4</v>
+        <v>17.5</v>
       </c>
       <c r="I22" s="23" t="n">
-        <v>4890</v>
+        <v>7434</v>
       </c>
       <c r="J22" s="24" t="n">
-        <v>51.7</v>
+        <v>80.5</v>
       </c>
       <c r="K22" s="24" t="n">
-        <v>5448</v>
+        <v>34198</v>
       </c>
       <c r="L22" s="25" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="M22" s="25" t="n">
-        <v>211</v>
+        <v>255</v>
       </c>
       <c r="N22" s="26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O22" s="26" t="n">
-        <v>0</v>
+        <v>552</v>
       </c>
       <c r="P22" s="27" t="n">
-        <v>53.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="Q22" s="27" t="n">
-        <v>5659</v>
-      </c>
-      <c r="R22" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S22" s="22" t="inlineStr"/>
-      <c r="T22" s="22" t="inlineStr"/>
-      <c r="U22" s="22" t="inlineStr"/>
-      <c r="V22" s="22" t="inlineStr"/>
-      <c r="W22" s="35" t="inlineStr"/>
+        <v>35005</v>
+      </c>
+      <c r="R22" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="21" t="n"/>
@@ -3990,7 +4906,7 @@
       <c r="D23" s="21" t="n"/>
       <c r="E23" s="22" t="inlineStr">
         <is>
-          <t>SO2101</t>
+          <t>SO2501</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -3999,48 +4915,43 @@
         </is>
       </c>
       <c r="G23" s="22" t="n">
-        <v>33529</v>
+        <v>16004</v>
       </c>
       <c r="H23" s="23" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I23" s="23" t="n">
-        <v>1744</v>
+        <v>1472</v>
       </c>
       <c r="J23" s="24" t="n">
-        <v>88.59999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="K23" s="24" t="n">
-        <v>29707</v>
+        <v>13795</v>
       </c>
       <c r="L23" s="25" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="M23" s="25" t="n">
-        <v>1609</v>
+        <v>144</v>
       </c>
       <c r="N23" s="26" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="O23" s="26" t="n">
-        <v>503</v>
+        <v>592</v>
       </c>
       <c r="P23" s="27" t="n">
-        <v>94.90000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="Q23" s="27" t="n">
-        <v>31819</v>
-      </c>
-      <c r="R23" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S23" s="22" t="inlineStr"/>
-      <c r="T23" s="22" t="inlineStr"/>
-      <c r="U23" s="22" t="inlineStr"/>
-      <c r="V23" s="22" t="inlineStr"/>
-      <c r="W23" s="35" t="inlineStr"/>
+        <v>14531</v>
+      </c>
+      <c r="R23" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="21" t="n"/>
@@ -4049,7 +4960,7 @@
       <c r="D24" s="21" t="n"/>
       <c r="E24" s="22" t="inlineStr">
         <is>
-          <t>SO2203</t>
+          <t>SO2601</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -4058,48 +4969,43 @@
         </is>
       </c>
       <c r="G24" s="22" t="n">
-        <v>247922</v>
+        <v>17317</v>
       </c>
       <c r="H24" s="23" t="n">
-        <v>31.4</v>
+        <v>4.5</v>
       </c>
       <c r="I24" s="23" t="n">
-        <v>77848</v>
+        <v>779</v>
       </c>
       <c r="J24" s="24" t="n">
-        <v>68.2</v>
+        <v>81.3</v>
       </c>
       <c r="K24" s="24" t="n">
-        <v>169083</v>
+        <v>14078</v>
       </c>
       <c r="L24" s="25" t="n">
-        <v>0.3</v>
+        <v>12.5</v>
       </c>
       <c r="M24" s="25" t="n">
-        <v>744</v>
+        <v>2165</v>
       </c>
       <c r="N24" s="26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O24" s="26" t="n">
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="P24" s="27" t="n">
-        <v>68.5</v>
+        <v>95.5</v>
       </c>
       <c r="Q24" s="27" t="n">
-        <v>169827</v>
-      </c>
-      <c r="R24" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S24" s="22" t="inlineStr"/>
-      <c r="T24" s="22" t="inlineStr"/>
-      <c r="U24" s="22" t="inlineStr"/>
-      <c r="V24" s="22" t="inlineStr"/>
-      <c r="W24" s="35" t="inlineStr"/>
+        <v>16537</v>
+      </c>
+      <c r="R24" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="21" t="n"/>
@@ -4108,7 +5014,7 @@
       <c r="D25" s="21" t="n"/>
       <c r="E25" s="22" t="inlineStr">
         <is>
-          <t>SO2210</t>
+          <t>SO2801</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -4117,48 +5023,43 @@
         </is>
       </c>
       <c r="G25" s="22" t="n">
-        <v>171981</v>
+        <v>37478</v>
       </c>
       <c r="H25" s="23" t="n">
-        <v>35.8</v>
+        <v>52.5</v>
       </c>
       <c r="I25" s="23" t="n">
-        <v>61569</v>
+        <v>19676</v>
       </c>
       <c r="J25" s="24" t="n">
-        <v>59.8</v>
+        <v>27.3</v>
       </c>
       <c r="K25" s="24" t="n">
-        <v>102845</v>
+        <v>10232</v>
       </c>
       <c r="L25" s="25" t="n">
-        <v>3.7</v>
+        <v>14.1</v>
       </c>
       <c r="M25" s="25" t="n">
-        <v>6363</v>
+        <v>5284</v>
       </c>
       <c r="N25" s="26" t="n">
-        <v>0.7</v>
+        <v>6.1</v>
       </c>
       <c r="O25" s="26" t="n">
-        <v>1204</v>
+        <v>2286</v>
       </c>
       <c r="P25" s="27" t="n">
-        <v>64.2</v>
+        <v>47.5</v>
       </c>
       <c r="Q25" s="27" t="n">
-        <v>110412</v>
-      </c>
-      <c r="R25" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S25" s="22" t="inlineStr"/>
-      <c r="T25" s="22" t="inlineStr"/>
-      <c r="U25" s="22" t="inlineStr"/>
-      <c r="V25" s="22" t="inlineStr"/>
-      <c r="W25" s="35" t="inlineStr"/>
+        <v>17802</v>
+      </c>
+      <c r="R25" s="28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="21" t="n"/>
@@ -4167,7 +5068,7 @@
       <c r="D26" s="21" t="n"/>
       <c r="E26" s="22" t="inlineStr">
         <is>
-          <t>SO2301</t>
+          <t>SO2802</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -4176,48 +5077,43 @@
         </is>
       </c>
       <c r="G26" s="22" t="n">
-        <v>60213</v>
+        <v>52658</v>
       </c>
       <c r="H26" s="23" t="n">
-        <v>61.1</v>
+        <v>85.8</v>
       </c>
       <c r="I26" s="23" t="n">
-        <v>36790</v>
+        <v>45180</v>
       </c>
       <c r="J26" s="24" t="n">
-        <v>38.3</v>
+        <v>11.5</v>
       </c>
       <c r="K26" s="24" t="n">
-        <v>23061</v>
+        <v>6056</v>
       </c>
       <c r="L26" s="25" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="M26" s="25" t="n">
-        <v>181</v>
+        <v>1211</v>
       </c>
       <c r="N26" s="26" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="O26" s="26" t="n">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="P26" s="27" t="n">
-        <v>38.9</v>
+        <v>14.2</v>
       </c>
       <c r="Q26" s="27" t="n">
-        <v>23423</v>
-      </c>
-      <c r="R26" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S26" s="22" t="inlineStr"/>
-      <c r="T26" s="22" t="inlineStr"/>
-      <c r="U26" s="22" t="inlineStr"/>
-      <c r="V26" s="22" t="inlineStr"/>
-      <c r="W26" s="35" t="inlineStr"/>
+        <v>7477</v>
+      </c>
+      <c r="R26" s="28" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="21" t="n"/>
@@ -4226,7 +5122,7 @@
       <c r="D27" s="21" t="n"/>
       <c r="E27" s="22" t="inlineStr">
         <is>
-          <t>SO2302</t>
+          <t>SO2803</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -4235,48 +5131,43 @@
         </is>
       </c>
       <c r="G27" s="22" t="n">
-        <v>67918</v>
+        <v>7176</v>
       </c>
       <c r="H27" s="23" t="n">
-        <v>15.1</v>
+        <v>55</v>
       </c>
       <c r="I27" s="23" t="n">
-        <v>10256</v>
+        <v>3947</v>
       </c>
       <c r="J27" s="24" t="n">
-        <v>82.5</v>
+        <v>40</v>
       </c>
       <c r="K27" s="24" t="n">
-        <v>56032</v>
+        <v>2870</v>
       </c>
       <c r="L27" s="25" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="M27" s="25" t="n">
-        <v>340</v>
+        <v>237</v>
       </c>
       <c r="N27" s="26" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="O27" s="26" t="n">
-        <v>1290</v>
+        <v>122</v>
       </c>
       <c r="P27" s="27" t="n">
-        <v>84.90000000000001</v>
+        <v>45</v>
       </c>
       <c r="Q27" s="27" t="n">
-        <v>57662</v>
-      </c>
-      <c r="R27" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S27" s="22" t="inlineStr"/>
-      <c r="T27" s="22" t="inlineStr"/>
-      <c r="U27" s="22" t="inlineStr"/>
-      <c r="V27" s="22" t="inlineStr"/>
-      <c r="W27" s="35" t="inlineStr"/>
+        <v>3229</v>
+      </c>
+      <c r="R27" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="21" t="n"/>
@@ -4285,7 +5176,7 @@
       <c r="D28" s="21" t="n"/>
       <c r="E28" s="22" t="inlineStr">
         <is>
-          <t>SO2401</t>
+          <t>SO2804</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -4294,48 +5185,43 @@
         </is>
       </c>
       <c r="G28" s="22" t="n">
-        <v>156304</v>
+        <v>47753</v>
       </c>
       <c r="H28" s="23" t="n">
-        <v>37.1</v>
+        <v>2.4</v>
       </c>
       <c r="I28" s="23" t="n">
-        <v>57989</v>
+        <v>1146</v>
       </c>
       <c r="J28" s="24" t="n">
-        <v>57.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>90500</v>
+        <v>31469</v>
       </c>
       <c r="L28" s="25" t="n">
-        <v>3.6</v>
+        <v>19.5</v>
       </c>
       <c r="M28" s="25" t="n">
-        <v>5627</v>
+        <v>9312</v>
       </c>
       <c r="N28" s="26" t="n">
-        <v>1.4</v>
+        <v>12.2</v>
       </c>
       <c r="O28" s="26" t="n">
-        <v>2188</v>
+        <v>5826</v>
       </c>
       <c r="P28" s="27" t="n">
-        <v>62.9</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q28" s="27" t="n">
-        <v>98315</v>
-      </c>
-      <c r="R28" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S28" s="22" t="inlineStr"/>
-      <c r="T28" s="22" t="inlineStr"/>
-      <c r="U28" s="22" t="inlineStr"/>
-      <c r="V28" s="22" t="inlineStr"/>
-      <c r="W28" s="35" t="inlineStr"/>
+        <v>46607</v>
+      </c>
+      <c r="R28" s="28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="21" t="n"/>
@@ -4344,7 +5230,7 @@
       <c r="D29" s="21" t="n"/>
       <c r="E29" s="22" t="inlineStr">
         <is>
-          <t>SO2402</t>
+          <t>SO1103</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -4353,48 +5239,43 @@
         </is>
       </c>
       <c r="G29" s="22" t="n">
-        <v>38531</v>
+        <v>17071</v>
       </c>
       <c r="H29" s="23" t="n">
-        <v>27.5</v>
+        <v>40.8</v>
       </c>
       <c r="I29" s="23" t="n">
-        <v>10596</v>
+        <v>6965</v>
       </c>
       <c r="J29" s="24" t="n">
-        <v>64.59999999999999</v>
+        <v>53.5</v>
       </c>
       <c r="K29" s="24" t="n">
-        <v>24891</v>
+        <v>9133</v>
       </c>
       <c r="L29" s="25" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="M29" s="25" t="n">
-        <v>655</v>
+        <v>717</v>
       </c>
       <c r="N29" s="26" t="n">
-        <v>6.2</v>
+        <v>1.4</v>
       </c>
       <c r="O29" s="26" t="n">
-        <v>2389</v>
+        <v>239</v>
       </c>
       <c r="P29" s="27" t="n">
-        <v>72.5</v>
+        <v>59.1</v>
       </c>
       <c r="Q29" s="27" t="n">
-        <v>27935</v>
-      </c>
-      <c r="R29" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S29" s="22" t="inlineStr"/>
-      <c r="T29" s="22" t="inlineStr"/>
-      <c r="U29" s="22" t="inlineStr"/>
-      <c r="V29" s="22" t="inlineStr"/>
-      <c r="W29" s="35" t="inlineStr"/>
+        <v>10089</v>
+      </c>
+      <c r="R29" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="21" t="n"/>
@@ -4403,7 +5284,7 @@
       <c r="D30" s="21" t="n"/>
       <c r="E30" s="22" t="inlineStr">
         <is>
-          <t>SO2403</t>
+          <t>SO1104</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -4412,48 +5293,43 @@
         </is>
       </c>
       <c r="G30" s="22" t="n">
-        <v>26900</v>
+        <v>15492</v>
       </c>
       <c r="H30" s="23" t="n">
-        <v>5.4</v>
+        <v>37.8</v>
       </c>
       <c r="I30" s="23" t="n">
-        <v>1453</v>
+        <v>5856</v>
       </c>
       <c r="J30" s="24" t="n">
-        <v>89.59999999999999</v>
+        <v>55.2</v>
       </c>
       <c r="K30" s="24" t="n">
-        <v>24102</v>
+        <v>8552</v>
       </c>
       <c r="L30" s="25" t="n">
-        <v>0.3</v>
+        <v>7</v>
       </c>
       <c r="M30" s="25" t="n">
-        <v>81</v>
+        <v>1084</v>
       </c>
       <c r="N30" s="26" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O30" s="26" t="n">
-        <v>1291</v>
+        <v>0</v>
       </c>
       <c r="P30" s="27" t="n">
-        <v>94.7</v>
+        <v>62.2</v>
       </c>
       <c r="Q30" s="27" t="n">
-        <v>25474</v>
-      </c>
-      <c r="R30" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S30" s="22" t="inlineStr"/>
-      <c r="T30" s="22" t="inlineStr"/>
-      <c r="U30" s="22" t="inlineStr"/>
-      <c r="V30" s="22" t="inlineStr"/>
-      <c r="W30" s="35" t="inlineStr"/>
+        <v>9636</v>
+      </c>
+      <c r="R30" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="21" t="n"/>
@@ -4462,7 +5338,7 @@
       <c r="D31" s="21" t="n"/>
       <c r="E31" s="22" t="inlineStr">
         <is>
-          <t>SO2404</t>
+          <t>SO1202</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -4471,48 +5347,43 @@
         </is>
       </c>
       <c r="G31" s="22" t="n">
-        <v>24608</v>
+        <v>36044</v>
       </c>
       <c r="H31" s="23" t="n">
-        <v>55.5</v>
+        <v>82.8</v>
       </c>
       <c r="I31" s="23" t="n">
-        <v>13658</v>
+        <v>29845</v>
       </c>
       <c r="J31" s="24" t="n">
-        <v>40.2</v>
+        <v>15.7</v>
       </c>
       <c r="K31" s="24" t="n">
-        <v>9893</v>
+        <v>5659</v>
       </c>
       <c r="L31" s="25" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="M31" s="25" t="n">
-        <v>345</v>
+        <v>433</v>
       </c>
       <c r="N31" s="26" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
       <c r="O31" s="26" t="n">
-        <v>714</v>
+        <v>108</v>
       </c>
       <c r="P31" s="27" t="n">
-        <v>44.5</v>
+        <v>17.2</v>
       </c>
       <c r="Q31" s="27" t="n">
-        <v>10951</v>
-      </c>
-      <c r="R31" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S31" s="22" t="inlineStr"/>
-      <c r="T31" s="22" t="inlineStr"/>
-      <c r="U31" s="22" t="inlineStr"/>
-      <c r="V31" s="22" t="inlineStr"/>
-      <c r="W31" s="35" t="inlineStr"/>
+        <v>6200</v>
+      </c>
+      <c r="R31" s="28" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="21" t="n"/>
@@ -4521,7 +5392,7 @@
       <c r="D32" s="21" t="n"/>
       <c r="E32" s="22" t="inlineStr">
         <is>
-          <t>SO2504</t>
+          <t>SO1304</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -4530,25 +5401,25 @@
         </is>
       </c>
       <c r="G32" s="22" t="n">
-        <v>14254</v>
+        <v>23365</v>
       </c>
       <c r="H32" s="23" t="n">
-        <v>55.8</v>
+        <v>42.9</v>
       </c>
       <c r="I32" s="23" t="n">
-        <v>7954</v>
+        <v>10024</v>
       </c>
       <c r="J32" s="24" t="n">
-        <v>44.2</v>
+        <v>47.2</v>
       </c>
       <c r="K32" s="24" t="n">
-        <v>6300</v>
+        <v>11028</v>
       </c>
       <c r="L32" s="25" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M32" s="25" t="n">
-        <v>0</v>
+        <v>2290</v>
       </c>
       <c r="N32" s="26" t="n">
         <v>0</v>
@@ -4557,21 +5428,16 @@
         <v>0</v>
       </c>
       <c r="P32" s="27" t="n">
-        <v>44.2</v>
+        <v>57</v>
       </c>
       <c r="Q32" s="27" t="n">
-        <v>6300</v>
-      </c>
-      <c r="R32" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S32" s="22" t="inlineStr"/>
-      <c r="T32" s="22" t="inlineStr"/>
-      <c r="U32" s="22" t="inlineStr"/>
-      <c r="V32" s="22" t="inlineStr"/>
-      <c r="W32" s="35" t="inlineStr"/>
+        <v>13318</v>
+      </c>
+      <c r="R32" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="21" t="n"/>
@@ -4580,7 +5446,7 @@
       <c r="D33" s="21" t="n"/>
       <c r="E33" s="22" t="inlineStr">
         <is>
-          <t>SO2602</t>
+          <t>SO1501</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -4589,48 +5455,43 @@
         </is>
       </c>
       <c r="G33" s="22" t="n">
-        <v>26103</v>
+        <v>31394</v>
       </c>
       <c r="H33" s="23" t="n">
-        <v>42.4</v>
+        <v>41.8</v>
       </c>
       <c r="I33" s="23" t="n">
-        <v>11068</v>
+        <v>13123</v>
       </c>
       <c r="J33" s="24" t="n">
-        <v>53.2</v>
+        <v>55.3</v>
       </c>
       <c r="K33" s="24" t="n">
-        <v>13887</v>
+        <v>17361</v>
       </c>
       <c r="L33" s="25" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="M33" s="25" t="n">
-        <v>626</v>
+        <v>659</v>
       </c>
       <c r="N33" s="26" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="O33" s="26" t="n">
-        <v>522</v>
+        <v>251</v>
       </c>
       <c r="P33" s="27" t="n">
-        <v>57.6</v>
+        <v>58.2</v>
       </c>
       <c r="Q33" s="27" t="n">
-        <v>15035</v>
-      </c>
-      <c r="R33" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S33" s="22" t="inlineStr"/>
-      <c r="T33" s="22" t="inlineStr"/>
-      <c r="U33" s="22" t="inlineStr"/>
-      <c r="V33" s="22" t="inlineStr"/>
-      <c r="W33" s="35" t="inlineStr"/>
+        <v>18271</v>
+      </c>
+      <c r="R33" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="21" t="n"/>
@@ -4639,7 +5500,7 @@
       <c r="D34" s="21" t="n"/>
       <c r="E34" s="22" t="inlineStr">
         <is>
-          <t>SO2603</t>
+          <t>SO1503</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -4648,48 +5509,43 @@
         </is>
       </c>
       <c r="G34" s="22" t="n">
-        <v>4845</v>
+        <v>32784</v>
       </c>
       <c r="H34" s="23" t="n">
-        <v>17.9</v>
+        <v>25.4</v>
       </c>
       <c r="I34" s="23" t="n">
-        <v>867</v>
+        <v>8327</v>
       </c>
       <c r="J34" s="24" t="n">
-        <v>71</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K34" s="24" t="n">
-        <v>3440</v>
+        <v>23965</v>
       </c>
       <c r="L34" s="25" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="M34" s="25" t="n">
-        <v>131</v>
+        <v>525</v>
       </c>
       <c r="N34" s="26" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="O34" s="26" t="n">
-        <v>407</v>
+        <v>0</v>
       </c>
       <c r="P34" s="27" t="n">
-        <v>82.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="Q34" s="27" t="n">
-        <v>3978</v>
-      </c>
-      <c r="R34" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S34" s="22" t="inlineStr"/>
-      <c r="T34" s="22" t="inlineStr"/>
-      <c r="U34" s="22" t="inlineStr"/>
-      <c r="V34" s="22" t="inlineStr"/>
-      <c r="W34" s="35" t="inlineStr"/>
+        <v>24490</v>
+      </c>
+      <c r="R34" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="21" t="n"/>
@@ -4698,7 +5554,7 @@
       <c r="D35" s="21" t="n"/>
       <c r="E35" s="22" t="inlineStr">
         <is>
-          <t>SO2604</t>
+          <t>SO1604</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -4707,48 +5563,43 @@
         </is>
       </c>
       <c r="G35" s="22" t="n">
-        <v>9533</v>
+        <v>9184</v>
       </c>
       <c r="H35" s="23" t="n">
-        <v>9.5</v>
+        <v>44</v>
       </c>
       <c r="I35" s="23" t="n">
-        <v>906</v>
+        <v>4041</v>
       </c>
       <c r="J35" s="24" t="n">
-        <v>76.59999999999999</v>
+        <v>48.2</v>
       </c>
       <c r="K35" s="24" t="n">
-        <v>7302</v>
+        <v>4427</v>
       </c>
       <c r="L35" s="25" t="n">
-        <v>12.4</v>
+        <v>7.8</v>
       </c>
       <c r="M35" s="25" t="n">
-        <v>1182</v>
+        <v>716</v>
       </c>
       <c r="N35" s="26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O35" s="26" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="P35" s="27" t="n">
-        <v>90.5</v>
+        <v>56</v>
       </c>
       <c r="Q35" s="27" t="n">
-        <v>8627</v>
-      </c>
-      <c r="R35" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S35" s="22" t="inlineStr"/>
-      <c r="T35" s="22" t="inlineStr"/>
-      <c r="U35" s="22" t="inlineStr"/>
-      <c r="V35" s="22" t="inlineStr"/>
-      <c r="W35" s="35" t="inlineStr"/>
+        <v>5143</v>
+      </c>
+      <c r="R35" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="21" t="n"/>
@@ -4757,7 +5608,7 @@
       <c r="D36" s="21" t="n"/>
       <c r="E36" s="22" t="inlineStr">
         <is>
-          <t>SO2605</t>
+          <t>SO1701</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -4766,111 +5617,1343 @@
         </is>
       </c>
       <c r="G36" s="22" t="n">
-        <v>30168</v>
+        <v>61170</v>
       </c>
       <c r="H36" s="23" t="n">
-        <v>45.6</v>
+        <v>53.7</v>
       </c>
       <c r="I36" s="23" t="n">
-        <v>13757</v>
+        <v>32848</v>
       </c>
       <c r="J36" s="24" t="n">
-        <v>36.1</v>
+        <v>45.3</v>
       </c>
       <c r="K36" s="24" t="n">
-        <v>10891</v>
+        <v>27710</v>
       </c>
       <c r="L36" s="25" t="n">
-        <v>15.7</v>
+        <v>0</v>
       </c>
       <c r="M36" s="25" t="n">
-        <v>4736</v>
+        <v>0</v>
       </c>
       <c r="N36" s="26" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="O36" s="26" t="n">
-        <v>784</v>
+        <v>612</v>
       </c>
       <c r="P36" s="27" t="n">
-        <v>54.4</v>
+        <v>46.3</v>
       </c>
       <c r="Q36" s="27" t="n">
-        <v>16412</v>
-      </c>
-      <c r="R36" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S36" s="22" t="inlineStr"/>
-      <c r="T36" s="22" t="inlineStr"/>
-      <c r="U36" s="22" t="inlineStr"/>
-      <c r="V36" s="22" t="inlineStr"/>
-      <c r="W36" s="35" t="inlineStr"/>
+        <v>28322</v>
+      </c>
+      <c r="R36" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="21" t="n"/>
       <c r="B37" s="21" t="n"/>
       <c r="C37" s="21" t="n"/>
       <c r="D37" s="21" t="n"/>
-      <c r="E37" s="29" t="inlineStr">
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>SO1801</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="n">
+        <v>182675</v>
+      </c>
+      <c r="H37" s="23" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="I37" s="23" t="n">
+        <v>92433</v>
+      </c>
+      <c r="J37" s="24" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="K37" s="24" t="n">
+        <v>75079</v>
+      </c>
+      <c r="L37" s="25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M37" s="25" t="n">
+        <v>6028</v>
+      </c>
+      <c r="N37" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="O37" s="26" t="n">
+        <v>9134</v>
+      </c>
+      <c r="P37" s="27" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="Q37" s="27" t="n">
+        <v>90241</v>
+      </c>
+      <c r="R37" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="21" t="n"/>
+      <c r="B38" s="21" t="n"/>
+      <c r="C38" s="21" t="n"/>
+      <c r="D38" s="21" t="n"/>
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>SO1802</t>
+        </is>
+      </c>
+      <c r="F38" s="22" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="n">
+        <v>35703</v>
+      </c>
+      <c r="H38" s="23" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="I38" s="23" t="n">
+        <v>25206</v>
+      </c>
+      <c r="J38" s="24" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="K38" s="24" t="n">
+        <v>10140</v>
+      </c>
+      <c r="L38" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" s="25" t="n">
+        <v>357</v>
+      </c>
+      <c r="N38" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="27" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="Q38" s="27" t="n">
+        <v>10497</v>
+      </c>
+      <c r="R38" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="21" t="n"/>
+      <c r="B39" s="21" t="n"/>
+      <c r="C39" s="21" t="n"/>
+      <c r="D39" s="21" t="n"/>
+      <c r="E39" s="22" t="inlineStr">
+        <is>
+          <t>SO1803</t>
+        </is>
+      </c>
+      <c r="F39" s="22" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="G39" s="22" t="n">
+        <v>46864</v>
+      </c>
+      <c r="H39" s="23" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="I39" s="23" t="n">
+        <v>16543</v>
+      </c>
+      <c r="J39" s="24" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="K39" s="24" t="n">
+        <v>29477</v>
+      </c>
+      <c r="L39" s="25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M39" s="25" t="n">
+        <v>844</v>
+      </c>
+      <c r="N39" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="27" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="Q39" s="27" t="n">
+        <v>30321</v>
+      </c>
+      <c r="R39" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="n"/>
+      <c r="B40" s="21" t="n"/>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="22" t="inlineStr">
+        <is>
+          <t>SO1901</t>
+        </is>
+      </c>
+      <c r="F40" s="22" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="G40" s="22" t="n">
+        <v>64063</v>
+      </c>
+      <c r="H40" s="23" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I40" s="23" t="n">
+        <v>16144</v>
+      </c>
+      <c r="J40" s="24" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="K40" s="24" t="n">
+        <v>38502</v>
+      </c>
+      <c r="L40" s="25" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M40" s="25" t="n">
+        <v>9417</v>
+      </c>
+      <c r="N40" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="27" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="Q40" s="27" t="n">
+        <v>47919</v>
+      </c>
+      <c r="R40" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="n"/>
+      <c r="B41" s="21" t="n"/>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="22" t="inlineStr">
+        <is>
+          <t>SO1902</t>
+        </is>
+      </c>
+      <c r="F41" s="22" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="G41" s="22" t="n">
+        <v>50364</v>
+      </c>
+      <c r="H41" s="23" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="I41" s="23" t="n">
+        <v>23067</v>
+      </c>
+      <c r="J41" s="24" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="K41" s="24" t="n">
+        <v>26088</v>
+      </c>
+      <c r="L41" s="25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M41" s="25" t="n">
+        <v>1058</v>
+      </c>
+      <c r="N41" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O41" s="26" t="n">
+        <v>201</v>
+      </c>
+      <c r="P41" s="27" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="Q41" s="27" t="n">
+        <v>27348</v>
+      </c>
+      <c r="R41" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="21" t="n"/>
+      <c r="B42" s="21" t="n"/>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="22" t="inlineStr">
+        <is>
+          <t>SO1903</t>
+        </is>
+      </c>
+      <c r="F42" s="22" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="G42" s="22" t="n">
+        <v>34105</v>
+      </c>
+      <c r="H42" s="23" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="I42" s="23" t="n">
+        <v>12244</v>
+      </c>
+      <c r="J42" s="24" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="K42" s="24" t="n">
+        <v>21248</v>
+      </c>
+      <c r="L42" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M42" s="25" t="n">
+        <v>171</v>
+      </c>
+      <c r="N42" s="26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O42" s="26" t="n">
+        <v>477</v>
+      </c>
+      <c r="P42" s="27" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="Q42" s="27" t="n">
+        <v>21896</v>
+      </c>
+      <c r="R42" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="21" t="n"/>
+      <c r="B43" s="21" t="n"/>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="22" t="inlineStr">
+        <is>
+          <t>SO2001</t>
+        </is>
+      </c>
+      <c r="F43" s="22" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="G43" s="22" t="n">
+        <v>48711</v>
+      </c>
+      <c r="H43" s="23" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="I43" s="23" t="n">
+        <v>17195</v>
+      </c>
+      <c r="J43" s="24" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="K43" s="24" t="n">
+        <v>30493</v>
+      </c>
+      <c r="L43" s="25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M43" s="25" t="n">
+        <v>877</v>
+      </c>
+      <c r="N43" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O43" s="26" t="n">
+        <v>146</v>
+      </c>
+      <c r="P43" s="27" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="Q43" s="27" t="n">
+        <v>31516</v>
+      </c>
+      <c r="R43" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="21" t="n"/>
+      <c r="B44" s="21" t="n"/>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="22" t="inlineStr">
+        <is>
+          <t>SO2002</t>
+        </is>
+      </c>
+      <c r="F44" s="22" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="G44" s="22" t="n">
+        <v>11508</v>
+      </c>
+      <c r="H44" s="23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I44" s="23" t="n">
+        <v>483</v>
+      </c>
+      <c r="J44" s="24" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="K44" s="24" t="n">
+        <v>9586</v>
+      </c>
+      <c r="L44" s="25" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="M44" s="25" t="n">
+        <v>1220</v>
+      </c>
+      <c r="N44" s="26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O44" s="26" t="n">
+        <v>219</v>
+      </c>
+      <c r="P44" s="27" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="Q44" s="27" t="n">
+        <v>11025</v>
+      </c>
+      <c r="R44" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="n"/>
+      <c r="B45" s="21" t="n"/>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="22" t="inlineStr">
+        <is>
+          <t>SO2003</t>
+        </is>
+      </c>
+      <c r="F45" s="22" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="G45" s="22" t="n">
+        <v>10539</v>
+      </c>
+      <c r="H45" s="23" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="I45" s="23" t="n">
+        <v>4890</v>
+      </c>
+      <c r="J45" s="24" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="K45" s="24" t="n">
+        <v>5448</v>
+      </c>
+      <c r="L45" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M45" s="25" t="n">
+        <v>211</v>
+      </c>
+      <c r="N45" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="27" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="Q45" s="27" t="n">
+        <v>5659</v>
+      </c>
+      <c r="R45" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="21" t="n"/>
+      <c r="B46" s="21" t="n"/>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="22" t="inlineStr">
+        <is>
+          <t>SO2101</t>
+        </is>
+      </c>
+      <c r="F46" s="22" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="G46" s="22" t="n">
+        <v>33529</v>
+      </c>
+      <c r="H46" s="23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I46" s="23" t="n">
+        <v>1744</v>
+      </c>
+      <c r="J46" s="24" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="K46" s="24" t="n">
+        <v>29707</v>
+      </c>
+      <c r="L46" s="25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M46" s="25" t="n">
+        <v>1609</v>
+      </c>
+      <c r="N46" s="26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O46" s="26" t="n">
+        <v>503</v>
+      </c>
+      <c r="P46" s="27" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="Q46" s="27" t="n">
+        <v>31819</v>
+      </c>
+      <c r="R46" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="21" t="n"/>
+      <c r="B47" s="21" t="n"/>
+      <c r="C47" s="21" t="n"/>
+      <c r="D47" s="21" t="n"/>
+      <c r="E47" s="22" t="inlineStr">
+        <is>
+          <t>SO2203</t>
+        </is>
+      </c>
+      <c r="F47" s="22" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="G47" s="22" t="n">
+        <v>247922</v>
+      </c>
+      <c r="H47" s="23" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="I47" s="23" t="n">
+        <v>77848</v>
+      </c>
+      <c r="J47" s="24" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="K47" s="24" t="n">
+        <v>169083</v>
+      </c>
+      <c r="L47" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M47" s="25" t="n">
+        <v>744</v>
+      </c>
+      <c r="N47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="27" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="Q47" s="27" t="n">
+        <v>169827</v>
+      </c>
+      <c r="R47" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="21" t="n"/>
+      <c r="B48" s="21" t="n"/>
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="21" t="n"/>
+      <c r="E48" s="22" t="inlineStr">
+        <is>
+          <t>SO2210</t>
+        </is>
+      </c>
+      <c r="F48" s="22" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="G48" s="22" t="n">
+        <v>171981</v>
+      </c>
+      <c r="H48" s="23" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="I48" s="23" t="n">
+        <v>61569</v>
+      </c>
+      <c r="J48" s="24" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="K48" s="24" t="n">
+        <v>102845</v>
+      </c>
+      <c r="L48" s="25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M48" s="25" t="n">
+        <v>6363</v>
+      </c>
+      <c r="N48" s="26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O48" s="26" t="n">
+        <v>1204</v>
+      </c>
+      <c r="P48" s="27" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="Q48" s="27" t="n">
+        <v>110412</v>
+      </c>
+      <c r="R48" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="21" t="n"/>
+      <c r="B49" s="21" t="n"/>
+      <c r="C49" s="21" t="n"/>
+      <c r="D49" s="21" t="n"/>
+      <c r="E49" s="22" t="inlineStr">
+        <is>
+          <t>SO2301</t>
+        </is>
+      </c>
+      <c r="F49" s="22" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="G49" s="22" t="n">
+        <v>60213</v>
+      </c>
+      <c r="H49" s="23" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="I49" s="23" t="n">
+        <v>36790</v>
+      </c>
+      <c r="J49" s="24" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="K49" s="24" t="n">
+        <v>23061</v>
+      </c>
+      <c r="L49" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M49" s="25" t="n">
+        <v>181</v>
+      </c>
+      <c r="N49" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O49" s="26" t="n">
+        <v>181</v>
+      </c>
+      <c r="P49" s="27" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="Q49" s="27" t="n">
+        <v>23423</v>
+      </c>
+      <c r="R49" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="21" t="n"/>
+      <c r="B50" s="21" t="n"/>
+      <c r="C50" s="21" t="n"/>
+      <c r="D50" s="21" t="n"/>
+      <c r="E50" s="22" t="inlineStr">
+        <is>
+          <t>SO2302</t>
+        </is>
+      </c>
+      <c r="F50" s="22" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="G50" s="22" t="n">
+        <v>67918</v>
+      </c>
+      <c r="H50" s="23" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="I50" s="23" t="n">
+        <v>10256</v>
+      </c>
+      <c r="J50" s="24" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="K50" s="24" t="n">
+        <v>56032</v>
+      </c>
+      <c r="L50" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M50" s="25" t="n">
+        <v>340</v>
+      </c>
+      <c r="N50" s="26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O50" s="26" t="n">
+        <v>1290</v>
+      </c>
+      <c r="P50" s="27" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="Q50" s="27" t="n">
+        <v>57662</v>
+      </c>
+      <c r="R50" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="21" t="n"/>
+      <c r="B51" s="21" t="n"/>
+      <c r="C51" s="21" t="n"/>
+      <c r="D51" s="21" t="n"/>
+      <c r="E51" s="22" t="inlineStr">
+        <is>
+          <t>SO2401</t>
+        </is>
+      </c>
+      <c r="F51" s="22" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="G51" s="22" t="n">
+        <v>156304</v>
+      </c>
+      <c r="H51" s="23" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="I51" s="23" t="n">
+        <v>57989</v>
+      </c>
+      <c r="J51" s="24" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="K51" s="24" t="n">
+        <v>90500</v>
+      </c>
+      <c r="L51" s="25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M51" s="25" t="n">
+        <v>5627</v>
+      </c>
+      <c r="N51" s="26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O51" s="26" t="n">
+        <v>2188</v>
+      </c>
+      <c r="P51" s="27" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="Q51" s="27" t="n">
+        <v>98315</v>
+      </c>
+      <c r="R51" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="21" t="n"/>
+      <c r="B52" s="21" t="n"/>
+      <c r="C52" s="21" t="n"/>
+      <c r="D52" s="21" t="n"/>
+      <c r="E52" s="22" t="inlineStr">
+        <is>
+          <t>SO2402</t>
+        </is>
+      </c>
+      <c r="F52" s="22" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="G52" s="22" t="n">
+        <v>38531</v>
+      </c>
+      <c r="H52" s="23" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="I52" s="23" t="n">
+        <v>10596</v>
+      </c>
+      <c r="J52" s="24" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="K52" s="24" t="n">
+        <v>24891</v>
+      </c>
+      <c r="L52" s="25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M52" s="25" t="n">
+        <v>655</v>
+      </c>
+      <c r="N52" s="26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O52" s="26" t="n">
+        <v>2389</v>
+      </c>
+      <c r="P52" s="27" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="Q52" s="27" t="n">
+        <v>27935</v>
+      </c>
+      <c r="R52" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="21" t="n"/>
+      <c r="B53" s="21" t="n"/>
+      <c r="C53" s="21" t="n"/>
+      <c r="D53" s="21" t="n"/>
+      <c r="E53" s="22" t="inlineStr">
+        <is>
+          <t>SO2403</t>
+        </is>
+      </c>
+      <c r="F53" s="22" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="G53" s="22" t="n">
+        <v>26900</v>
+      </c>
+      <c r="H53" s="23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I53" s="23" t="n">
+        <v>1453</v>
+      </c>
+      <c r="J53" s="24" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="K53" s="24" t="n">
+        <v>24102</v>
+      </c>
+      <c r="L53" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M53" s="25" t="n">
+        <v>81</v>
+      </c>
+      <c r="N53" s="26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O53" s="26" t="n">
+        <v>1291</v>
+      </c>
+      <c r="P53" s="27" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="Q53" s="27" t="n">
+        <v>25474</v>
+      </c>
+      <c r="R53" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="21" t="n"/>
+      <c r="B54" s="21" t="n"/>
+      <c r="C54" s="21" t="n"/>
+      <c r="D54" s="21" t="n"/>
+      <c r="E54" s="22" t="inlineStr">
+        <is>
+          <t>SO2404</t>
+        </is>
+      </c>
+      <c r="F54" s="22" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="G54" s="22" t="n">
+        <v>24608</v>
+      </c>
+      <c r="H54" s="23" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="I54" s="23" t="n">
+        <v>13658</v>
+      </c>
+      <c r="J54" s="24" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="K54" s="24" t="n">
+        <v>9893</v>
+      </c>
+      <c r="L54" s="25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M54" s="25" t="n">
+        <v>345</v>
+      </c>
+      <c r="N54" s="26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O54" s="26" t="n">
+        <v>714</v>
+      </c>
+      <c r="P54" s="27" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="Q54" s="27" t="n">
+        <v>10951</v>
+      </c>
+      <c r="R54" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="21" t="n"/>
+      <c r="B55" s="21" t="n"/>
+      <c r="C55" s="21" t="n"/>
+      <c r="D55" s="21" t="n"/>
+      <c r="E55" s="22" t="inlineStr">
+        <is>
+          <t>SO2504</t>
+        </is>
+      </c>
+      <c r="F55" s="22" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="G55" s="22" t="n">
+        <v>14254</v>
+      </c>
+      <c r="H55" s="23" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="I55" s="23" t="n">
+        <v>7954</v>
+      </c>
+      <c r="J55" s="24" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="K55" s="24" t="n">
+        <v>6300</v>
+      </c>
+      <c r="L55" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="27" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="Q55" s="27" t="n">
+        <v>6300</v>
+      </c>
+      <c r="R55" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="21" t="n"/>
+      <c r="B56" s="21" t="n"/>
+      <c r="C56" s="21" t="n"/>
+      <c r="D56" s="21" t="n"/>
+      <c r="E56" s="22" t="inlineStr">
+        <is>
+          <t>SO2602</t>
+        </is>
+      </c>
+      <c r="F56" s="22" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="G56" s="22" t="n">
+        <v>26103</v>
+      </c>
+      <c r="H56" s="23" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="I56" s="23" t="n">
+        <v>11068</v>
+      </c>
+      <c r="J56" s="24" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="K56" s="24" t="n">
+        <v>13887</v>
+      </c>
+      <c r="L56" s="25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M56" s="25" t="n">
+        <v>626</v>
+      </c>
+      <c r="N56" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="O56" s="26" t="n">
+        <v>522</v>
+      </c>
+      <c r="P56" s="27" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="Q56" s="27" t="n">
+        <v>15035</v>
+      </c>
+      <c r="R56" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="21" t="n"/>
+      <c r="B57" s="21" t="n"/>
+      <c r="C57" s="21" t="n"/>
+      <c r="D57" s="21" t="n"/>
+      <c r="E57" s="22" t="inlineStr">
+        <is>
+          <t>SO2603</t>
+        </is>
+      </c>
+      <c r="F57" s="22" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="G57" s="22" t="n">
+        <v>4845</v>
+      </c>
+      <c r="H57" s="23" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I57" s="23" t="n">
+        <v>867</v>
+      </c>
+      <c r="J57" s="24" t="n">
+        <v>71</v>
+      </c>
+      <c r="K57" s="24" t="n">
+        <v>3440</v>
+      </c>
+      <c r="L57" s="25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M57" s="25" t="n">
+        <v>131</v>
+      </c>
+      <c r="N57" s="26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="O57" s="26" t="n">
+        <v>407</v>
+      </c>
+      <c r="P57" s="27" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="Q57" s="27" t="n">
+        <v>3978</v>
+      </c>
+      <c r="R57" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="21" t="n"/>
+      <c r="B58" s="21" t="n"/>
+      <c r="C58" s="21" t="n"/>
+      <c r="D58" s="21" t="n"/>
+      <c r="E58" s="22" t="inlineStr">
+        <is>
+          <t>SO2604</t>
+        </is>
+      </c>
+      <c r="F58" s="22" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="G58" s="22" t="n">
+        <v>9533</v>
+      </c>
+      <c r="H58" s="23" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I58" s="23" t="n">
+        <v>906</v>
+      </c>
+      <c r="J58" s="24" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="K58" s="24" t="n">
+        <v>7302</v>
+      </c>
+      <c r="L58" s="25" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="M58" s="25" t="n">
+        <v>1182</v>
+      </c>
+      <c r="N58" s="26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O58" s="26" t="n">
+        <v>143</v>
+      </c>
+      <c r="P58" s="27" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="Q58" s="27" t="n">
+        <v>8627</v>
+      </c>
+      <c r="R58" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="21" t="n"/>
+      <c r="B59" s="21" t="n"/>
+      <c r="C59" s="21" t="n"/>
+      <c r="D59" s="21" t="n"/>
+      <c r="E59" s="22" t="inlineStr">
+        <is>
+          <t>SO2605</t>
+        </is>
+      </c>
+      <c r="F59" s="22" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="G59" s="22" t="n">
+        <v>30168</v>
+      </c>
+      <c r="H59" s="23" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="I59" s="23" t="n">
+        <v>13757</v>
+      </c>
+      <c r="J59" s="24" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="K59" s="24" t="n">
+        <v>10891</v>
+      </c>
+      <c r="L59" s="25" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="M59" s="25" t="n">
+        <v>4736</v>
+      </c>
+      <c r="N59" s="26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O59" s="26" t="n">
+        <v>784</v>
+      </c>
+      <c r="P59" s="27" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="Q59" s="27" t="n">
+        <v>16412</v>
+      </c>
+      <c r="R59" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="21" t="n"/>
+      <c r="B60" s="21" t="n"/>
+      <c r="C60" s="21" t="n"/>
+      <c r="D60" s="21" t="n"/>
+      <c r="E60" s="29" t="inlineStr">
         <is>
           <t>SO2606</t>
         </is>
       </c>
-      <c r="F37" s="29" t="inlineStr">
+      <c r="F60" s="29" t="inlineStr">
         <is>
           <t>host</t>
         </is>
       </c>
-      <c r="G37" s="29" t="n">
+      <c r="G60" s="29" t="n">
         <v>5019</v>
       </c>
-      <c r="H37" s="30" t="n">
+      <c r="H60" s="30" t="n">
         <v>42.5</v>
       </c>
-      <c r="I37" s="30" t="n">
+      <c r="I60" s="30" t="n">
         <v>2133</v>
       </c>
-      <c r="J37" s="31" t="n">
+      <c r="J60" s="31" t="n">
         <v>53.7</v>
       </c>
-      <c r="K37" s="31" t="n">
+      <c r="K60" s="31" t="n">
         <v>2695</v>
       </c>
-      <c r="L37" s="32" t="n">
+      <c r="L60" s="32" t="n">
         <v>3.5</v>
       </c>
-      <c r="M37" s="32" t="n">
+      <c r="M60" s="32" t="n">
         <v>176</v>
       </c>
-      <c r="N37" s="33" t="n">
+      <c r="N60" s="33" t="n">
         <v>0.3</v>
       </c>
-      <c r="O37" s="33" t="n">
+      <c r="O60" s="33" t="n">
         <v>15</v>
       </c>
-      <c r="P37" s="34" t="n">
+      <c r="P60" s="34" t="n">
         <v>57.5</v>
       </c>
-      <c r="Q37" s="34" t="n">
+      <c r="Q60" s="34" t="n">
         <v>2886</v>
       </c>
-      <c r="R37" s="34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S37" s="29" t="inlineStr"/>
-      <c r="T37" s="29" t="inlineStr"/>
-      <c r="U37" s="29" t="inlineStr"/>
-      <c r="V37" s="29" t="inlineStr"/>
-      <c r="W37" s="35" t="inlineStr"/>
+      <c r="R60" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="E1:W1"/>
+    <mergeCell ref="E1:R1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4882,7 +6965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W33"/>
+  <dimension ref="A1:R42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="5" max="5"/>
@@ -4899,11 +6982,6 @@
     <col width="33" customWidth="1" min="16" max="16"/>
     <col width="33" customWidth="1" min="17" max="17"/>
     <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="47" customWidth="1" min="20" max="20"/>
-    <col width="44" customWidth="1" min="21" max="21"/>
-    <col width="44" customWidth="1" min="22" max="22"/>
-    <col width="44" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4991,31 +7069,6 @@
           <t>Area severity</t>
         </is>
       </c>
-      <c r="S5" s="15" t="inlineStr">
-        <is>
-          <t>Admin_Pcode_2024</t>
-        </is>
-      </c>
-      <c r="T5" s="15" t="inlineStr">
-        <is>
-          <t>%_severity_levels_1-2_2024_extrapolation_base</t>
-        </is>
-      </c>
-      <c r="U5" s="15" t="inlineStr">
-        <is>
-          <t>%_severity_level_3_2024_extrapolation_base</t>
-        </is>
-      </c>
-      <c r="V5" s="15" t="inlineStr">
-        <is>
-          <t>%_severity_level_4_2024_extrapolation_base</t>
-        </is>
-      </c>
-      <c r="W5" s="15" t="inlineStr">
-        <is>
-          <t>%_severity_level_5_2024_extrapolation_base</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="21" t="n"/>
@@ -5024,7 +7077,7 @@
       <c r="D6" s="21" t="n"/>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>SO1103</t>
+          <t>SO1401</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -5033,48 +7086,43 @@
         </is>
       </c>
       <c r="G6" s="22" t="n">
-        <v>15</v>
+        <v>1759</v>
       </c>
       <c r="H6" s="23" t="n">
-        <v>34.3</v>
+        <v>21.3</v>
       </c>
       <c r="I6" s="23" t="n">
-        <v>5</v>
+        <v>375</v>
       </c>
       <c r="J6" s="24" t="n">
-        <v>61.3</v>
+        <v>77.2</v>
       </c>
       <c r="K6" s="24" t="n">
-        <v>9</v>
+        <v>1358</v>
       </c>
       <c r="L6" s="25" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="M6" s="25" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="N6" s="26" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="O6" s="26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P6" s="27" t="n">
-        <v>65.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="Q6" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="R6" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S6" s="22" t="inlineStr"/>
-      <c r="T6" s="22" t="inlineStr"/>
-      <c r="U6" s="22" t="inlineStr"/>
-      <c r="V6" s="22" t="inlineStr"/>
-      <c r="W6" s="35" t="inlineStr"/>
+        <v>1384</v>
+      </c>
+      <c r="R6" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="21" t="n"/>
@@ -5083,7 +7131,7 @@
       <c r="D7" s="21" t="n"/>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>SO1202</t>
+          <t>SO1601</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -5092,48 +7140,43 @@
         </is>
       </c>
       <c r="G7" s="22" t="n">
-        <v>0</v>
+        <v>6989</v>
       </c>
       <c r="H7" s="23" t="n">
-        <v>80.3</v>
+        <v>24.5</v>
       </c>
       <c r="I7" s="23" t="n">
-        <v>0</v>
+        <v>1712</v>
       </c>
       <c r="J7" s="24" t="n">
-        <v>17.1</v>
+        <v>74</v>
       </c>
       <c r="K7" s="24" t="n">
-        <v>0</v>
+        <v>5172</v>
       </c>
       <c r="L7" s="25" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="M7" s="25" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="N7" s="26" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O7" s="26" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="P7" s="27" t="n">
-        <v>19.7</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="Q7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="27" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="S7" s="22" t="inlineStr"/>
-      <c r="T7" s="22" t="inlineStr"/>
-      <c r="U7" s="22" t="inlineStr"/>
-      <c r="V7" s="22" t="inlineStr"/>
-      <c r="W7" s="35" t="inlineStr"/>
+        <v>5284</v>
+      </c>
+      <c r="R7" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="21" t="n"/>
@@ -5142,7 +7185,7 @@
       <c r="D8" s="21" t="n"/>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>SO1501</t>
+          <t>SO1606</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -5151,48 +7194,43 @@
         </is>
       </c>
       <c r="G8" s="22" t="n">
-        <v>5944</v>
+        <v>2560</v>
       </c>
       <c r="H8" s="23" t="n">
-        <v>37.9</v>
+        <v>28.7</v>
       </c>
       <c r="I8" s="23" t="n">
-        <v>2253</v>
+        <v>735</v>
       </c>
       <c r="J8" s="24" t="n">
-        <v>54.3</v>
+        <v>60.8</v>
       </c>
       <c r="K8" s="24" t="n">
-        <v>3228</v>
+        <v>1556</v>
       </c>
       <c r="L8" s="25" t="n">
-        <v>1.7</v>
+        <v>9.5</v>
       </c>
       <c r="M8" s="25" t="n">
-        <v>101</v>
+        <v>243</v>
       </c>
       <c r="N8" s="26" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O8" s="26" t="n">
-        <v>357</v>
+        <v>26</v>
       </c>
       <c r="P8" s="27" t="n">
-        <v>62</v>
+        <v>71.3</v>
       </c>
       <c r="Q8" s="27" t="n">
-        <v>3685</v>
-      </c>
-      <c r="R8" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S8" s="22" t="inlineStr"/>
-      <c r="T8" s="22" t="inlineStr"/>
-      <c r="U8" s="22" t="inlineStr"/>
-      <c r="V8" s="22" t="inlineStr"/>
-      <c r="W8" s="35" t="inlineStr"/>
+        <v>1825</v>
+      </c>
+      <c r="R8" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="21" t="n"/>
@@ -5201,7 +7239,7 @@
       <c r="D9" s="21" t="n"/>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>SO1701</t>
+          <t>SO2103</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -5210,48 +7248,43 @@
         </is>
       </c>
       <c r="G9" s="22" t="n">
-        <v>3884</v>
+        <v>10543</v>
       </c>
       <c r="H9" s="23" t="n">
-        <v>22.1</v>
+        <v>33</v>
       </c>
       <c r="I9" s="23" t="n">
-        <v>858</v>
+        <v>3479</v>
       </c>
       <c r="J9" s="24" t="n">
-        <v>76.5</v>
+        <v>60.2</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>2971</v>
+        <v>6347</v>
       </c>
       <c r="L9" s="25" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="M9" s="25" t="n">
-        <v>27</v>
+        <v>242</v>
       </c>
       <c r="N9" s="26" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="O9" s="26" t="n">
-        <v>27</v>
+        <v>474</v>
       </c>
       <c r="P9" s="27" t="n">
-        <v>77.90000000000001</v>
+        <v>67</v>
       </c>
       <c r="Q9" s="27" t="n">
-        <v>3026</v>
-      </c>
-      <c r="R9" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S9" s="22" t="inlineStr"/>
-      <c r="T9" s="22" t="inlineStr"/>
-      <c r="U9" s="22" t="inlineStr"/>
-      <c r="V9" s="22" t="inlineStr"/>
-      <c r="W9" s="35" t="inlineStr"/>
+        <v>7064</v>
+      </c>
+      <c r="R9" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="21" t="n"/>
@@ -5260,7 +7293,7 @@
       <c r="D10" s="21" t="n"/>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>SO1801</t>
+          <t>SO2303</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -5269,48 +7302,43 @@
         </is>
       </c>
       <c r="G10" s="22" t="n">
-        <v>11678</v>
+        <v>0</v>
       </c>
       <c r="H10" s="23" t="n">
-        <v>22.3</v>
+        <v>52.6</v>
       </c>
       <c r="I10" s="23" t="n">
-        <v>2604</v>
+        <v>0</v>
       </c>
       <c r="J10" s="24" t="n">
-        <v>63.6</v>
+        <v>38.2</v>
       </c>
       <c r="K10" s="24" t="n">
-        <v>7427</v>
+        <v>0</v>
       </c>
       <c r="L10" s="25" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="M10" s="25" t="n">
-        <v>1039</v>
+        <v>0</v>
       </c>
       <c r="N10" s="26" t="n">
-        <v>5.2</v>
+        <v>0.2</v>
       </c>
       <c r="O10" s="26" t="n">
-        <v>607</v>
+        <v>0</v>
       </c>
       <c r="P10" s="27" t="n">
-        <v>77.7</v>
+        <v>47.4</v>
       </c>
       <c r="Q10" s="27" t="n">
-        <v>9074</v>
-      </c>
-      <c r="R10" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S10" s="22" t="inlineStr"/>
-      <c r="T10" s="22" t="inlineStr"/>
-      <c r="U10" s="22" t="inlineStr"/>
-      <c r="V10" s="22" t="inlineStr"/>
-      <c r="W10" s="35" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R10" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="21" t="n"/>
@@ -5319,7 +7347,7 @@
       <c r="D11" s="21" t="n"/>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>SO1802</t>
+          <t>SO2307</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -5328,48 +7356,43 @@
         </is>
       </c>
       <c r="G11" s="22" t="n">
-        <v>1518</v>
+        <v>191</v>
       </c>
       <c r="H11" s="23" t="n">
-        <v>49.2</v>
+        <v>27.8</v>
       </c>
       <c r="I11" s="23" t="n">
-        <v>747</v>
+        <v>53</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>44.2</v>
+        <v>40.6</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>671</v>
+        <v>78</v>
       </c>
       <c r="L11" s="25" t="n">
-        <v>5.4</v>
+        <v>29.4</v>
       </c>
       <c r="M11" s="25" t="n">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="N11" s="26" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="O11" s="26" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="P11" s="27" t="n">
-        <v>50.9</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="Q11" s="27" t="n">
-        <v>773</v>
-      </c>
-      <c r="R11" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S11" s="22" t="inlineStr"/>
-      <c r="T11" s="22" t="inlineStr"/>
-      <c r="U11" s="22" t="inlineStr"/>
-      <c r="V11" s="22" t="inlineStr"/>
-      <c r="W11" s="35" t="inlineStr"/>
+        <v>138</v>
+      </c>
+      <c r="R11" s="28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="21" t="n"/>
@@ -5378,7 +7401,7 @@
       <c r="D12" s="21" t="n"/>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>SO1803</t>
+          <t>SO2601</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -5387,48 +7410,43 @@
         </is>
       </c>
       <c r="G12" s="22" t="n">
-        <v>63</v>
+        <v>1515</v>
       </c>
       <c r="H12" s="23" t="n">
-        <v>44.9</v>
+        <v>0</v>
       </c>
       <c r="I12" s="23" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J12" s="24" t="n">
-        <v>54.5</v>
+        <v>67.3</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>34</v>
+        <v>1020</v>
       </c>
       <c r="L12" s="25" t="n">
-        <v>0.6</v>
+        <v>24.5</v>
       </c>
       <c r="M12" s="25" t="n">
-        <v>0</v>
+        <v>371</v>
       </c>
       <c r="N12" s="26" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O12" s="26" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="P12" s="27" t="n">
-        <v>55.1</v>
+        <v>100</v>
       </c>
       <c r="Q12" s="27" t="n">
-        <v>35</v>
-      </c>
-      <c r="R12" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S12" s="22" t="inlineStr"/>
-      <c r="T12" s="22" t="inlineStr"/>
-      <c r="U12" s="22" t="inlineStr"/>
-      <c r="V12" s="22" t="inlineStr"/>
-      <c r="W12" s="35" t="inlineStr"/>
+        <v>1515</v>
+      </c>
+      <c r="R12" s="28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="21" t="n"/>
@@ -5437,7 +7455,7 @@
       <c r="D13" s="21" t="n"/>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t>SO1901</t>
+          <t>SO2801</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -5446,48 +7464,43 @@
         </is>
       </c>
       <c r="G13" s="22" t="n">
-        <v>490</v>
+        <v>6746</v>
       </c>
       <c r="H13" s="23" t="n">
-        <v>43.9</v>
+        <v>21</v>
       </c>
       <c r="I13" s="23" t="n">
-        <v>215</v>
+        <v>1417</v>
       </c>
       <c r="J13" s="24" t="n">
-        <v>50.5</v>
+        <v>60</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>247</v>
+        <v>4047</v>
       </c>
       <c r="L13" s="25" t="n">
-        <v>5.6</v>
+        <v>17.2</v>
       </c>
       <c r="M13" s="25" t="n">
-        <v>27</v>
+        <v>1160</v>
       </c>
       <c r="N13" s="26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O13" s="26" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P13" s="27" t="n">
-        <v>56.1</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="Q13" s="27" t="n">
-        <v>275</v>
-      </c>
-      <c r="R13" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S13" s="22" t="inlineStr"/>
-      <c r="T13" s="22" t="inlineStr"/>
-      <c r="U13" s="22" t="inlineStr"/>
-      <c r="V13" s="22" t="inlineStr"/>
-      <c r="W13" s="35" t="inlineStr"/>
+        <v>5336</v>
+      </c>
+      <c r="R13" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="21" t="n"/>
@@ -5496,7 +7509,7 @@
       <c r="D14" s="21" t="n"/>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>SO1902</t>
+          <t>SO2802</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -5505,48 +7518,43 @@
         </is>
       </c>
       <c r="G14" s="22" t="n">
-        <v>1505</v>
+        <v>4821</v>
       </c>
       <c r="H14" s="23" t="n">
-        <v>40.4</v>
+        <v>2.3</v>
       </c>
       <c r="I14" s="23" t="n">
-        <v>608</v>
+        <v>111</v>
       </c>
       <c r="J14" s="24" t="n">
-        <v>56.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>853</v>
+        <v>3548</v>
       </c>
       <c r="L14" s="25" t="n">
-        <v>2.5</v>
+        <v>22.8</v>
       </c>
       <c r="M14" s="25" t="n">
-        <v>38</v>
+        <v>1099</v>
       </c>
       <c r="N14" s="26" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="O14" s="26" t="n">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="P14" s="27" t="n">
-        <v>59.6</v>
+        <v>97.7</v>
       </c>
       <c r="Q14" s="27" t="n">
-        <v>897</v>
-      </c>
-      <c r="R14" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S14" s="22" t="inlineStr"/>
-      <c r="T14" s="22" t="inlineStr"/>
-      <c r="U14" s="22" t="inlineStr"/>
-      <c r="V14" s="22" t="inlineStr"/>
-      <c r="W14" s="35" t="inlineStr"/>
+        <v>4710</v>
+      </c>
+      <c r="R14" s="28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="21" t="n"/>
@@ -5555,7 +7563,7 @@
       <c r="D15" s="21" t="n"/>
       <c r="E15" s="22" t="inlineStr">
         <is>
-          <t>SO1903</t>
+          <t>SO1103</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -5564,48 +7572,43 @@
         </is>
       </c>
       <c r="G15" s="22" t="n">
-        <v>187</v>
+        <v>15</v>
       </c>
       <c r="H15" s="23" t="n">
-        <v>48.3</v>
+        <v>34.3</v>
       </c>
       <c r="I15" s="23" t="n">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="J15" s="24" t="n">
-        <v>49.5</v>
+        <v>61.3</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>92</v>
+        <v>9</v>
       </c>
       <c r="L15" s="25" t="n">
-        <v>0.2</v>
+        <v>3.6</v>
       </c>
       <c r="M15" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="26" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="O15" s="26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P15" s="27" t="n">
-        <v>51.6</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="Q15" s="27" t="n">
-        <v>96</v>
-      </c>
-      <c r="R15" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S15" s="22" t="inlineStr"/>
-      <c r="T15" s="22" t="inlineStr"/>
-      <c r="U15" s="22" t="inlineStr"/>
-      <c r="V15" s="22" t="inlineStr"/>
-      <c r="W15" s="35" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="R15" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="21" t="n"/>
@@ -5614,7 +7617,7 @@
       <c r="D16" s="21" t="n"/>
       <c r="E16" s="22" t="inlineStr">
         <is>
-          <t>SO2001</t>
+          <t>SO1202</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -5623,25 +7626,25 @@
         </is>
       </c>
       <c r="G16" s="22" t="n">
-        <v>19148</v>
+        <v>0</v>
       </c>
       <c r="H16" s="23" t="n">
-        <v>17.9</v>
+        <v>80.3</v>
       </c>
       <c r="I16" s="23" t="n">
-        <v>3427</v>
+        <v>0</v>
       </c>
       <c r="J16" s="24" t="n">
-        <v>79.40000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>15203</v>
+        <v>0</v>
       </c>
       <c r="L16" s="25" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="M16" s="25" t="n">
-        <v>517</v>
+        <v>0</v>
       </c>
       <c r="N16" s="26" t="n">
         <v>0</v>
@@ -5650,21 +7653,16 @@
         <v>0</v>
       </c>
       <c r="P16" s="27" t="n">
-        <v>82.09999999999999</v>
+        <v>19.7</v>
       </c>
       <c r="Q16" s="27" t="n">
-        <v>15720</v>
-      </c>
-      <c r="R16" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S16" s="22" t="inlineStr"/>
-      <c r="T16" s="22" t="inlineStr"/>
-      <c r="U16" s="22" t="inlineStr"/>
-      <c r="V16" s="22" t="inlineStr"/>
-      <c r="W16" s="35" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R16" s="28" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="21" t="n"/>
@@ -5673,7 +7671,7 @@
       <c r="D17" s="21" t="n"/>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>SO2002</t>
+          <t>SO1501</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -5682,48 +7680,43 @@
         </is>
       </c>
       <c r="G17" s="22" t="n">
-        <v>5466</v>
+        <v>5944</v>
       </c>
       <c r="H17" s="23" t="n">
-        <v>23.1</v>
+        <v>37.9</v>
       </c>
       <c r="I17" s="23" t="n">
-        <v>1263</v>
+        <v>2253</v>
       </c>
       <c r="J17" s="24" t="n">
-        <v>74.40000000000001</v>
+        <v>54.3</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>4066</v>
+        <v>3228</v>
       </c>
       <c r="L17" s="25" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="M17" s="25" t="n">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="N17" s="26" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="O17" s="26" t="n">
-        <v>71</v>
+        <v>357</v>
       </c>
       <c r="P17" s="27" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="Q17" s="27" t="n">
-        <v>4209</v>
-      </c>
-      <c r="R17" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S17" s="22" t="inlineStr"/>
-      <c r="T17" s="22" t="inlineStr"/>
-      <c r="U17" s="22" t="inlineStr"/>
-      <c r="V17" s="22" t="inlineStr"/>
-      <c r="W17" s="35" t="inlineStr"/>
+        <v>3685</v>
+      </c>
+      <c r="R17" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="21" t="n"/>
@@ -5732,7 +7725,7 @@
       <c r="D18" s="21" t="n"/>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>SO2003</t>
+          <t>SO1701</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -5741,48 +7734,43 @@
         </is>
       </c>
       <c r="G18" s="22" t="n">
-        <v>383</v>
+        <v>3884</v>
       </c>
       <c r="H18" s="23" t="n">
-        <v>0.9</v>
+        <v>22.1</v>
       </c>
       <c r="I18" s="23" t="n">
-        <v>3</v>
+        <v>858</v>
       </c>
       <c r="J18" s="24" t="n">
-        <v>93.8</v>
+        <v>76.5</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>359</v>
+        <v>2971</v>
       </c>
       <c r="L18" s="25" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="M18" s="25" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="N18" s="26" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="O18" s="26" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="P18" s="27" t="n">
-        <v>99.09999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="Q18" s="27" t="n">
-        <v>379</v>
-      </c>
-      <c r="R18" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S18" s="22" t="inlineStr"/>
-      <c r="T18" s="22" t="inlineStr"/>
-      <c r="U18" s="22" t="inlineStr"/>
-      <c r="V18" s="22" t="inlineStr"/>
-      <c r="W18" s="35" t="inlineStr"/>
+        <v>3026</v>
+      </c>
+      <c r="R18" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="21" t="n"/>
@@ -5791,7 +7779,7 @@
       <c r="D19" s="21" t="n"/>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>SO2101</t>
+          <t>SO1801</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -5800,48 +7788,43 @@
         </is>
       </c>
       <c r="G19" s="22" t="n">
-        <v>23519</v>
+        <v>11678</v>
       </c>
       <c r="H19" s="23" t="n">
-        <v>1.4</v>
+        <v>22.3</v>
       </c>
       <c r="I19" s="23" t="n">
-        <v>329</v>
+        <v>2604</v>
       </c>
       <c r="J19" s="24" t="n">
-        <v>93.09999999999999</v>
+        <v>63.6</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>21896</v>
+        <v>7427</v>
       </c>
       <c r="L19" s="25" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="M19" s="25" t="n">
+        <v>1039</v>
+      </c>
+      <c r="N19" s="26" t="n">
         <v>5.2</v>
       </c>
-      <c r="M19" s="25" t="n">
-        <v>1223</v>
-      </c>
-      <c r="N19" s="26" t="n">
-        <v>0.3</v>
-      </c>
       <c r="O19" s="26" t="n">
-        <v>71</v>
+        <v>607</v>
       </c>
       <c r="P19" s="27" t="n">
-        <v>98.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="Q19" s="27" t="n">
-        <v>23189</v>
-      </c>
-      <c r="R19" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S19" s="22" t="inlineStr"/>
-      <c r="T19" s="22" t="inlineStr"/>
-      <c r="U19" s="22" t="inlineStr"/>
-      <c r="V19" s="22" t="inlineStr"/>
-      <c r="W19" s="35" t="inlineStr"/>
+        <v>9074</v>
+      </c>
+      <c r="R19" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="21" t="n"/>
@@ -5850,7 +7833,7 @@
       <c r="D20" s="21" t="n"/>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>SO2203</t>
+          <t>SO1802</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -5859,48 +7842,43 @@
         </is>
       </c>
       <c r="G20" s="22" t="n">
-        <v>0</v>
+        <v>1518</v>
       </c>
       <c r="H20" s="23" t="n">
-        <v>11</v>
+        <v>49.2</v>
       </c>
       <c r="I20" s="23" t="n">
-        <v>0</v>
+        <v>747</v>
       </c>
       <c r="J20" s="24" t="n">
-        <v>88.59999999999999</v>
+        <v>44.2</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0</v>
+        <v>671</v>
       </c>
       <c r="L20" s="25" t="n">
-        <v>0.4</v>
+        <v>5.4</v>
       </c>
       <c r="M20" s="25" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="N20" s="26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O20" s="26" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P20" s="27" t="n">
-        <v>89</v>
+        <v>50.9</v>
       </c>
       <c r="Q20" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S20" s="22" t="inlineStr"/>
-      <c r="T20" s="22" t="inlineStr"/>
-      <c r="U20" s="22" t="inlineStr"/>
-      <c r="V20" s="22" t="inlineStr"/>
-      <c r="W20" s="35" t="inlineStr"/>
+        <v>773</v>
+      </c>
+      <c r="R20" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="21" t="n"/>
@@ -5909,7 +7887,7 @@
       <c r="D21" s="21" t="n"/>
       <c r="E21" s="22" t="inlineStr">
         <is>
-          <t>SO2210</t>
+          <t>SO1803</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -5918,22 +7896,22 @@
         </is>
       </c>
       <c r="G21" s="22" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H21" s="23" t="n">
-        <v>9.1</v>
+        <v>44.9</v>
       </c>
       <c r="I21" s="23" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J21" s="24" t="n">
-        <v>88</v>
+        <v>54.5</v>
       </c>
       <c r="K21" s="24" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L21" s="25" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="M21" s="25" t="n">
         <v>0</v>
@@ -5945,21 +7923,16 @@
         <v>0</v>
       </c>
       <c r="P21" s="27" t="n">
-        <v>90.90000000000001</v>
+        <v>55.1</v>
       </c>
       <c r="Q21" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S21" s="22" t="inlineStr"/>
-      <c r="T21" s="22" t="inlineStr"/>
-      <c r="U21" s="22" t="inlineStr"/>
-      <c r="V21" s="22" t="inlineStr"/>
-      <c r="W21" s="35" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="R21" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="21" t="n"/>
@@ -5968,7 +7941,7 @@
       <c r="D22" s="21" t="n"/>
       <c r="E22" s="22" t="inlineStr">
         <is>
-          <t>SO2301</t>
+          <t>SO1901</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -5977,25 +7950,25 @@
         </is>
       </c>
       <c r="G22" s="22" t="n">
-        <v>43</v>
+        <v>490</v>
       </c>
       <c r="H22" s="23" t="n">
-        <v>0</v>
+        <v>43.9</v>
       </c>
       <c r="I22" s="23" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="J22" s="24" t="n">
-        <v>100</v>
+        <v>50.5</v>
       </c>
       <c r="K22" s="24" t="n">
-        <v>43</v>
+        <v>247</v>
       </c>
       <c r="L22" s="25" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="M22" s="25" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="N22" s="26" t="n">
         <v>0</v>
@@ -6004,21 +7977,16 @@
         <v>0</v>
       </c>
       <c r="P22" s="27" t="n">
-        <v>100</v>
+        <v>56.1</v>
       </c>
       <c r="Q22" s="27" t="n">
-        <v>43</v>
-      </c>
-      <c r="R22" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S22" s="22" t="inlineStr"/>
-      <c r="T22" s="22" t="inlineStr"/>
-      <c r="U22" s="22" t="inlineStr"/>
-      <c r="V22" s="22" t="inlineStr"/>
-      <c r="W22" s="35" t="inlineStr"/>
+        <v>275</v>
+      </c>
+      <c r="R22" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="21" t="n"/>
@@ -6027,7 +7995,7 @@
       <c r="D23" s="21" t="n"/>
       <c r="E23" s="22" t="inlineStr">
         <is>
-          <t>SO2302</t>
+          <t>SO1902</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -6036,48 +8004,43 @@
         </is>
       </c>
       <c r="G23" s="22" t="n">
-        <v>6247</v>
+        <v>1505</v>
       </c>
       <c r="H23" s="23" t="n">
-        <v>1.4</v>
+        <v>40.4</v>
       </c>
       <c r="I23" s="23" t="n">
-        <v>87</v>
+        <v>608</v>
       </c>
       <c r="J23" s="24" t="n">
-        <v>97.09999999999999</v>
+        <v>56.7</v>
       </c>
       <c r="K23" s="24" t="n">
-        <v>6066</v>
+        <v>853</v>
       </c>
       <c r="L23" s="25" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="M23" s="25" t="n">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="N23" s="26" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O23" s="26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P23" s="27" t="n">
-        <v>98.5</v>
+        <v>59.6</v>
       </c>
       <c r="Q23" s="27" t="n">
-        <v>6153</v>
-      </c>
-      <c r="R23" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S23" s="22" t="inlineStr"/>
-      <c r="T23" s="22" t="inlineStr"/>
-      <c r="U23" s="22" t="inlineStr"/>
-      <c r="V23" s="22" t="inlineStr"/>
-      <c r="W23" s="35" t="inlineStr"/>
+        <v>897</v>
+      </c>
+      <c r="R23" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="21" t="n"/>
@@ -6086,7 +8049,7 @@
       <c r="D24" s="21" t="n"/>
       <c r="E24" s="22" t="inlineStr">
         <is>
-          <t>SO2401</t>
+          <t>SO1903</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -6095,48 +8058,43 @@
         </is>
       </c>
       <c r="G24" s="22" t="n">
-        <v>19897</v>
+        <v>187</v>
       </c>
       <c r="H24" s="23" t="n">
-        <v>24.7</v>
+        <v>48.3</v>
       </c>
       <c r="I24" s="23" t="n">
-        <v>4915</v>
+        <v>90</v>
       </c>
       <c r="J24" s="24" t="n">
-        <v>72.7</v>
+        <v>49.5</v>
       </c>
       <c r="K24" s="24" t="n">
-        <v>14465</v>
+        <v>92</v>
       </c>
       <c r="L24" s="25" t="n">
-        <v>2.6</v>
+        <v>0.2</v>
       </c>
       <c r="M24" s="25" t="n">
-        <v>517</v>
+        <v>0</v>
       </c>
       <c r="N24" s="26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O24" s="26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P24" s="27" t="n">
-        <v>75.3</v>
+        <v>51.6</v>
       </c>
       <c r="Q24" s="27" t="n">
-        <v>14983</v>
-      </c>
-      <c r="R24" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S24" s="22" t="inlineStr"/>
-      <c r="T24" s="22" t="inlineStr"/>
-      <c r="U24" s="22" t="inlineStr"/>
-      <c r="V24" s="22" t="inlineStr"/>
-      <c r="W24" s="35" t="inlineStr"/>
+        <v>96</v>
+      </c>
+      <c r="R24" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="21" t="n"/>
@@ -6145,7 +8103,7 @@
       <c r="D25" s="21" t="n"/>
       <c r="E25" s="22" t="inlineStr">
         <is>
-          <t>SO2402</t>
+          <t>SO2001</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -6154,48 +8112,43 @@
         </is>
       </c>
       <c r="G25" s="22" t="n">
-        <v>494</v>
+        <v>19148</v>
       </c>
       <c r="H25" s="23" t="n">
-        <v>0.6</v>
+        <v>17.9</v>
       </c>
       <c r="I25" s="23" t="n">
-        <v>3</v>
+        <v>3427</v>
       </c>
       <c r="J25" s="24" t="n">
-        <v>98.90000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K25" s="24" t="n">
-        <v>489</v>
+        <v>15203</v>
       </c>
       <c r="L25" s="25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M25" s="25" t="n">
-        <v>0</v>
+        <v>517</v>
       </c>
       <c r="N25" s="26" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="O25" s="26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P25" s="27" t="n">
-        <v>99.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="Q25" s="27" t="n">
-        <v>492</v>
-      </c>
-      <c r="R25" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S25" s="22" t="inlineStr"/>
-      <c r="T25" s="22" t="inlineStr"/>
-      <c r="U25" s="22" t="inlineStr"/>
-      <c r="V25" s="22" t="inlineStr"/>
-      <c r="W25" s="35" t="inlineStr"/>
+        <v>15720</v>
+      </c>
+      <c r="R25" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="21" t="n"/>
@@ -6204,7 +8157,7 @@
       <c r="D26" s="21" t="n"/>
       <c r="E26" s="22" t="inlineStr">
         <is>
-          <t>SO2403</t>
+          <t>SO2002</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -6213,48 +8166,43 @@
         </is>
       </c>
       <c r="G26" s="22" t="n">
-        <v>9197</v>
+        <v>5466</v>
       </c>
       <c r="H26" s="23" t="n">
-        <v>3.9</v>
+        <v>23.1</v>
       </c>
       <c r="I26" s="23" t="n">
-        <v>359</v>
+        <v>1263</v>
       </c>
       <c r="J26" s="24" t="n">
-        <v>90.90000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K26" s="24" t="n">
-        <v>8360</v>
+        <v>4066</v>
       </c>
       <c r="L26" s="25" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="M26" s="25" t="n">
-        <v>405</v>
+        <v>71</v>
       </c>
       <c r="N26" s="26" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="O26" s="26" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="P26" s="27" t="n">
-        <v>96.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="Q26" s="27" t="n">
-        <v>8839</v>
-      </c>
-      <c r="R26" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S26" s="22" t="inlineStr"/>
-      <c r="T26" s="22" t="inlineStr"/>
-      <c r="U26" s="22" t="inlineStr"/>
-      <c r="V26" s="22" t="inlineStr"/>
-      <c r="W26" s="35" t="inlineStr"/>
+        <v>4209</v>
+      </c>
+      <c r="R26" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="21" t="n"/>
@@ -6263,7 +8211,7 @@
       <c r="D27" s="21" t="n"/>
       <c r="E27" s="22" t="inlineStr">
         <is>
-          <t>SO2404</t>
+          <t>SO2003</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -6272,48 +8220,43 @@
         </is>
       </c>
       <c r="G27" s="22" t="n">
-        <v>6215</v>
+        <v>383</v>
       </c>
       <c r="H27" s="23" t="n">
-        <v>16.5</v>
+        <v>0.9</v>
       </c>
       <c r="I27" s="23" t="n">
-        <v>1025</v>
+        <v>3</v>
       </c>
       <c r="J27" s="24" t="n">
-        <v>74.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="K27" s="24" t="n">
-        <v>4655</v>
+        <v>359</v>
       </c>
       <c r="L27" s="25" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="M27" s="25" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="N27" s="26" t="n">
-        <v>7.9</v>
+        <v>1.8</v>
       </c>
       <c r="O27" s="26" t="n">
-        <v>491</v>
+        <v>7</v>
       </c>
       <c r="P27" s="27" t="n">
-        <v>83.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="Q27" s="27" t="n">
-        <v>5183</v>
-      </c>
-      <c r="R27" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S27" s="22" t="inlineStr"/>
-      <c r="T27" s="22" t="inlineStr"/>
-      <c r="U27" s="22" t="inlineStr"/>
-      <c r="V27" s="22" t="inlineStr"/>
-      <c r="W27" s="35" t="inlineStr"/>
+        <v>379</v>
+      </c>
+      <c r="R27" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="21" t="n"/>
@@ -6322,7 +8265,7 @@
       <c r="D28" s="21" t="n"/>
       <c r="E28" s="22" t="inlineStr">
         <is>
-          <t>SO2504</t>
+          <t>SO2101</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -6331,48 +8274,43 @@
         </is>
       </c>
       <c r="G28" s="22" t="n">
-        <v>3184</v>
+        <v>23519</v>
       </c>
       <c r="H28" s="23" t="n">
-        <v>48.5</v>
+        <v>1.4</v>
       </c>
       <c r="I28" s="23" t="n">
-        <v>1544</v>
+        <v>329</v>
       </c>
       <c r="J28" s="24" t="n">
-        <v>51.5</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>1640</v>
+        <v>21896</v>
       </c>
       <c r="L28" s="25" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="M28" s="25" t="n">
-        <v>0</v>
+        <v>1223</v>
       </c>
       <c r="N28" s="26" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O28" s="26" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="P28" s="27" t="n">
-        <v>51.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Q28" s="27" t="n">
-        <v>1640</v>
-      </c>
-      <c r="R28" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S28" s="22" t="inlineStr"/>
-      <c r="T28" s="22" t="inlineStr"/>
-      <c r="U28" s="22" t="inlineStr"/>
-      <c r="V28" s="22" t="inlineStr"/>
-      <c r="W28" s="35" t="inlineStr"/>
+        <v>23189</v>
+      </c>
+      <c r="R28" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="21" t="n"/>
@@ -6381,7 +8319,7 @@
       <c r="D29" s="21" t="n"/>
       <c r="E29" s="22" t="inlineStr">
         <is>
-          <t>SO2602</t>
+          <t>SO2203</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -6390,48 +8328,43 @@
         </is>
       </c>
       <c r="G29" s="22" t="n">
-        <v>11328</v>
+        <v>0</v>
       </c>
       <c r="H29" s="23" t="n">
-        <v>25.6</v>
+        <v>11</v>
       </c>
       <c r="I29" s="23" t="n">
-        <v>2900</v>
+        <v>0</v>
       </c>
       <c r="J29" s="24" t="n">
-        <v>64.59999999999999</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K29" s="24" t="n">
-        <v>7318</v>
+        <v>0</v>
       </c>
       <c r="L29" s="25" t="n">
-        <v>8.5</v>
+        <v>0.4</v>
       </c>
       <c r="M29" s="25" t="n">
-        <v>963</v>
+        <v>0</v>
       </c>
       <c r="N29" s="26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O29" s="26" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="P29" s="27" t="n">
-        <v>74.3</v>
+        <v>89</v>
       </c>
       <c r="Q29" s="27" t="n">
-        <v>8417</v>
-      </c>
-      <c r="R29" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S29" s="22" t="inlineStr"/>
-      <c r="T29" s="22" t="inlineStr"/>
-      <c r="U29" s="22" t="inlineStr"/>
-      <c r="V29" s="22" t="inlineStr"/>
-      <c r="W29" s="35" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R29" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="21" t="n"/>
@@ -6440,7 +8373,7 @@
       <c r="D30" s="21" t="n"/>
       <c r="E30" s="22" t="inlineStr">
         <is>
-          <t>SO2603</t>
+          <t>SO2210</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -6449,48 +8382,43 @@
         </is>
       </c>
       <c r="G30" s="22" t="n">
-        <v>13858</v>
+        <v>0</v>
       </c>
       <c r="H30" s="23" t="n">
-        <v>3.1</v>
+        <v>9.1</v>
       </c>
       <c r="I30" s="23" t="n">
-        <v>430</v>
+        <v>0</v>
       </c>
       <c r="J30" s="24" t="n">
-        <v>85.2</v>
+        <v>88</v>
       </c>
       <c r="K30" s="24" t="n">
-        <v>11807</v>
+        <v>0</v>
       </c>
       <c r="L30" s="25" t="n">
-        <v>6.8</v>
+        <v>2.9</v>
       </c>
       <c r="M30" s="25" t="n">
-        <v>942</v>
+        <v>0</v>
       </c>
       <c r="N30" s="26" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O30" s="26" t="n">
-        <v>679</v>
+        <v>0</v>
       </c>
       <c r="P30" s="27" t="n">
-        <v>96.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q30" s="27" t="n">
-        <v>13429</v>
-      </c>
-      <c r="R30" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S30" s="22" t="inlineStr"/>
-      <c r="T30" s="22" t="inlineStr"/>
-      <c r="U30" s="22" t="inlineStr"/>
-      <c r="V30" s="22" t="inlineStr"/>
-      <c r="W30" s="35" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R30" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="21" t="n"/>
@@ -6499,7 +8427,7 @@
       <c r="D31" s="21" t="n"/>
       <c r="E31" s="22" t="inlineStr">
         <is>
-          <t>SO2604</t>
+          <t>SO2301</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -6508,25 +8436,25 @@
         </is>
       </c>
       <c r="G31" s="22" t="n">
-        <v>316</v>
+        <v>43</v>
       </c>
       <c r="H31" s="23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J31" s="24" t="n">
-        <v>97.8</v>
+        <v>100</v>
       </c>
       <c r="K31" s="24" t="n">
-        <v>309</v>
+        <v>43</v>
       </c>
       <c r="L31" s="25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="M31" s="25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N31" s="26" t="n">
         <v>0</v>
@@ -6535,21 +8463,16 @@
         <v>0</v>
       </c>
       <c r="P31" s="27" t="n">
-        <v>98.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q31" s="27" t="n">
-        <v>313</v>
-      </c>
-      <c r="R31" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S31" s="22" t="inlineStr"/>
-      <c r="T31" s="22" t="inlineStr"/>
-      <c r="U31" s="22" t="inlineStr"/>
-      <c r="V31" s="22" t="inlineStr"/>
-      <c r="W31" s="35" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="R31" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="21" t="n"/>
@@ -6558,7 +8481,7 @@
       <c r="D32" s="21" t="n"/>
       <c r="E32" s="22" t="inlineStr">
         <is>
-          <t>SO2605</t>
+          <t>SO2302</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -6567,111 +8490,587 @@
         </is>
       </c>
       <c r="G32" s="22" t="n">
-        <v>10210</v>
+        <v>6247</v>
       </c>
       <c r="H32" s="23" t="n">
-        <v>36.3</v>
+        <v>1.4</v>
       </c>
       <c r="I32" s="23" t="n">
-        <v>3706</v>
+        <v>87</v>
       </c>
       <c r="J32" s="24" t="n">
-        <v>42.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="K32" s="24" t="n">
-        <v>4339</v>
+        <v>6066</v>
       </c>
       <c r="L32" s="25" t="n">
-        <v>20.1</v>
+        <v>1.4</v>
       </c>
       <c r="M32" s="25" t="n">
-        <v>2052</v>
+        <v>87</v>
       </c>
       <c r="N32" s="26" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="O32" s="26" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="P32" s="27" t="n">
-        <v>63.7</v>
+        <v>98.5</v>
       </c>
       <c r="Q32" s="27" t="n">
-        <v>6503</v>
-      </c>
-      <c r="R32" s="27" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S32" s="22" t="inlineStr"/>
-      <c r="T32" s="22" t="inlineStr"/>
-      <c r="U32" s="22" t="inlineStr"/>
-      <c r="V32" s="22" t="inlineStr"/>
-      <c r="W32" s="35" t="inlineStr"/>
+        <v>6153</v>
+      </c>
+      <c r="R32" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="21" t="n"/>
       <c r="B33" s="21" t="n"/>
       <c r="C33" s="21" t="n"/>
       <c r="D33" s="21" t="n"/>
-      <c r="E33" s="29" t="inlineStr">
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>SO2401</t>
+        </is>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="n">
+        <v>19897</v>
+      </c>
+      <c r="H33" s="23" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="I33" s="23" t="n">
+        <v>4915</v>
+      </c>
+      <c r="J33" s="24" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="K33" s="24" t="n">
+        <v>14465</v>
+      </c>
+      <c r="L33" s="25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M33" s="25" t="n">
+        <v>517</v>
+      </c>
+      <c r="N33" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="27" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="Q33" s="27" t="n">
+        <v>14983</v>
+      </c>
+      <c r="R33" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="n"/>
+      <c r="B34" s="21" t="n"/>
+      <c r="C34" s="21" t="n"/>
+      <c r="D34" s="21" t="n"/>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>SO2402</t>
+        </is>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="G34" s="22" t="n">
+        <v>494</v>
+      </c>
+      <c r="H34" s="23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I34" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" s="24" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="K34" s="24" t="n">
+        <v>489</v>
+      </c>
+      <c r="L34" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O34" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="P34" s="27" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="Q34" s="27" t="n">
+        <v>492</v>
+      </c>
+      <c r="R34" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="n"/>
+      <c r="B35" s="21" t="n"/>
+      <c r="C35" s="21" t="n"/>
+      <c r="D35" s="21" t="n"/>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>SO2403</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="n">
+        <v>9197</v>
+      </c>
+      <c r="H35" s="23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I35" s="23" t="n">
+        <v>359</v>
+      </c>
+      <c r="J35" s="24" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="K35" s="24" t="n">
+        <v>8360</v>
+      </c>
+      <c r="L35" s="25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M35" s="25" t="n">
+        <v>405</v>
+      </c>
+      <c r="N35" s="26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O35" s="26" t="n">
+        <v>74</v>
+      </c>
+      <c r="P35" s="27" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="Q35" s="27" t="n">
+        <v>8839</v>
+      </c>
+      <c r="R35" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="21" t="n"/>
+      <c r="B36" s="21" t="n"/>
+      <c r="C36" s="21" t="n"/>
+      <c r="D36" s="21" t="n"/>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>SO2404</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="n">
+        <v>6215</v>
+      </c>
+      <c r="H36" s="23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I36" s="23" t="n">
+        <v>1025</v>
+      </c>
+      <c r="J36" s="24" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="K36" s="24" t="n">
+        <v>4655</v>
+      </c>
+      <c r="L36" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M36" s="25" t="n">
+        <v>37</v>
+      </c>
+      <c r="N36" s="26" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="O36" s="26" t="n">
+        <v>491</v>
+      </c>
+      <c r="P36" s="27" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="Q36" s="27" t="n">
+        <v>5183</v>
+      </c>
+      <c r="R36" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="n"/>
+      <c r="B37" s="21" t="n"/>
+      <c r="C37" s="21" t="n"/>
+      <c r="D37" s="21" t="n"/>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>SO2504</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="n">
+        <v>3184</v>
+      </c>
+      <c r="H37" s="23" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="I37" s="23" t="n">
+        <v>1544</v>
+      </c>
+      <c r="J37" s="24" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="K37" s="24" t="n">
+        <v>1640</v>
+      </c>
+      <c r="L37" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="27" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="Q37" s="27" t="n">
+        <v>1640</v>
+      </c>
+      <c r="R37" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="21" t="n"/>
+      <c r="B38" s="21" t="n"/>
+      <c r="C38" s="21" t="n"/>
+      <c r="D38" s="21" t="n"/>
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>SO2602</t>
+        </is>
+      </c>
+      <c r="F38" s="22" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="n">
+        <v>11328</v>
+      </c>
+      <c r="H38" s="23" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="I38" s="23" t="n">
+        <v>2900</v>
+      </c>
+      <c r="J38" s="24" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="K38" s="24" t="n">
+        <v>7318</v>
+      </c>
+      <c r="L38" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M38" s="25" t="n">
+        <v>963</v>
+      </c>
+      <c r="N38" s="26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O38" s="26" t="n">
+        <v>136</v>
+      </c>
+      <c r="P38" s="27" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="Q38" s="27" t="n">
+        <v>8417</v>
+      </c>
+      <c r="R38" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="21" t="n"/>
+      <c r="B39" s="21" t="n"/>
+      <c r="C39" s="21" t="n"/>
+      <c r="D39" s="21" t="n"/>
+      <c r="E39" s="22" t="inlineStr">
+        <is>
+          <t>SO2603</t>
+        </is>
+      </c>
+      <c r="F39" s="22" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="G39" s="22" t="n">
+        <v>13858</v>
+      </c>
+      <c r="H39" s="23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I39" s="23" t="n">
+        <v>430</v>
+      </c>
+      <c r="J39" s="24" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="K39" s="24" t="n">
+        <v>11807</v>
+      </c>
+      <c r="L39" s="25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="M39" s="25" t="n">
+        <v>942</v>
+      </c>
+      <c r="N39" s="26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O39" s="26" t="n">
+        <v>679</v>
+      </c>
+      <c r="P39" s="27" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="Q39" s="27" t="n">
+        <v>13429</v>
+      </c>
+      <c r="R39" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="n"/>
+      <c r="B40" s="21" t="n"/>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="22" t="inlineStr">
+        <is>
+          <t>SO2604</t>
+        </is>
+      </c>
+      <c r="F40" s="22" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="G40" s="22" t="n">
+        <v>316</v>
+      </c>
+      <c r="H40" s="23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I40" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J40" s="24" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="K40" s="24" t="n">
+        <v>309</v>
+      </c>
+      <c r="L40" s="25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M40" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="N40" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="27" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="Q40" s="27" t="n">
+        <v>313</v>
+      </c>
+      <c r="R40" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="n"/>
+      <c r="B41" s="21" t="n"/>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="22" t="inlineStr">
+        <is>
+          <t>SO2605</t>
+        </is>
+      </c>
+      <c r="F41" s="22" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="G41" s="22" t="n">
+        <v>10210</v>
+      </c>
+      <c r="H41" s="23" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="I41" s="23" t="n">
+        <v>3706</v>
+      </c>
+      <c r="J41" s="24" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="K41" s="24" t="n">
+        <v>4339</v>
+      </c>
+      <c r="L41" s="25" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="M41" s="25" t="n">
+        <v>2052</v>
+      </c>
+      <c r="N41" s="26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O41" s="26" t="n">
+        <v>112</v>
+      </c>
+      <c r="P41" s="27" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="Q41" s="27" t="n">
+        <v>6503</v>
+      </c>
+      <c r="R41" s="28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="21" t="n"/>
+      <c r="B42" s="21" t="n"/>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="29" t="inlineStr">
         <is>
           <t>SO2606</t>
         </is>
       </c>
-      <c r="F33" s="29" t="inlineStr">
+      <c r="F42" s="29" t="inlineStr">
         <is>
           <t>IDP</t>
         </is>
       </c>
-      <c r="G33" s="29" t="n">
+      <c r="G42" s="29" t="n">
         <v>18724</v>
       </c>
-      <c r="H33" s="30" t="n">
+      <c r="H42" s="30" t="n">
         <v>11.7</v>
       </c>
-      <c r="I33" s="30" t="n">
+      <c r="I42" s="30" t="n">
         <v>2191</v>
       </c>
-      <c r="J33" s="31" t="n">
+      <c r="J42" s="31" t="n">
         <v>87</v>
       </c>
-      <c r="K33" s="31" t="n">
+      <c r="K42" s="31" t="n">
         <v>16290</v>
       </c>
-      <c r="L33" s="32" t="n">
+      <c r="L42" s="32" t="n">
         <v>1.4</v>
       </c>
-      <c r="M33" s="32" t="n">
+      <c r="M42" s="32" t="n">
         <v>262</v>
       </c>
-      <c r="N33" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="34" t="n">
+      <c r="N42" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="34" t="n">
         <v>88.40000000000001</v>
       </c>
-      <c r="Q33" s="34" t="n">
+      <c r="Q42" s="34" t="n">
         <v>16552</v>
       </c>
-      <c r="R33" s="34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S33" s="29" t="inlineStr"/>
-      <c r="T33" s="29" t="inlineStr"/>
-      <c r="U33" s="29" t="inlineStr"/>
-      <c r="V33" s="29" t="inlineStr"/>
-      <c r="W33" s="35" t="inlineStr"/>
+      <c r="R42" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="E1:W1"/>
+    <mergeCell ref="E1:R1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
